--- a/data/positions/Posição Consolidada - 5166121.xlsx
+++ b/data/positions/Posição Consolidada - 5166121.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 5166121 | 21/08/2026, 14:50</x:t>
+    <x:t>Conta: 5166121 | 25/08/2026, 19:23</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>55,9%|Operações Compromissadas</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 6.343.033,20</x:t>
+    <x:t>R$ 6.348.605,00</x:t>
   </x:si>
   <x:si>
     <x:t>55,80%|Pós-Fixada</x:t>
@@ -88,10 +88,10 @@
     <x:t>R$ 2.320.442,51</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.331.675,38</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.329.147,99</x:t>
+    <x:t>R$ 2.333.723,55</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.330.735,32</x:t>
   </x:si>
   <x:si>
     <x:t>07/08/2026</x:t>
@@ -103,10 +103,10 @@
     <x:t>R$ 1.999.048,84</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.007.844,23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.005.865,27</x:t>
+    <x:t>R$ 2.009.607,95</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.007.232,15</x:t>
   </x:si>
   <x:si>
     <x:t>17/08/2026</x:t>
@@ -121,16 +121,16 @@
     <x:t>R$ 1.999.998,41</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.003.513,59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.002.722,67</x:t>
+    <x:t>R$ 2.005.273,50</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.004.086,60</x:t>
   </x:si>
   <x:si>
     <x:t>44,1%|Fundos de Investimento</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 5.005.110,58</x:t>
+    <x:t>R$ 5.010.218,86</x:t>
   </x:si>
   <x:si>
     <x:t>44,10%|Fundos de Renda Fixa Pós-Fixado</x:t>
@@ -151,10 +151,10 @@
     <x:t>Safra DI Master FIRF Referenciado DI LP</x:t>
   </x:si>
   <x:si>
-    <x:t>20/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 271,88</x:t>
+    <x:t>24/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 272,16</x:t>
   </x:si>
   <x:si>
     <x:t>7.363,69</x:t>
@@ -163,28 +163,28 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.002.066,23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.000.112,10</x:t>
+    <x:t>R$ 2.004.067,02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.000.630,40</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
   </x:si>
   <x:si>
-    <x:t>21/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.439,63</x:t>
+    <x:t>25/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.441,09</x:t>
   </x:si>
   <x:si>
     <x:t>1.390,64</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.002.002,37</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.000.108,63</x:t>
+    <x:t>R$ 2.004.043,72</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.000.626,78</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
@@ -196,10 +196,10 @@
     <x:t>680.719,86</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.001.041,98</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.000.056,52</x:t>
+    <x:t>R$ 1.002.108,12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.000.326,76</x:t>
   </x:si>
   <x:si>
     <x:t>R$ 382,83</x:t>
@@ -840,10 +840,10 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>11348526.6076973</x:v>
+        <x:v>11359206.6880217</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>11348143.7776973</x:v>
+        <x:v>11358823.8580217</x:v>
       </x:c>
       <x:c r="C4" s="7">
         <x:v>382.83</x:v>

--- a/data/positions/Posição Consolidada - 5166121.xlsx
+++ b/data/positions/Posição Consolidada - 5166121.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 5166121 | 25/08/2026, 19:23</x:t>
+    <x:t>Conta: 5166121 | 28/08/2026, 09:33</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>55,9%|Operações Compromissadas</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 6.348.605,00</x:t>
+    <x:t>R$ 6.356.971,88</x:t>
   </x:si>
   <x:si>
     <x:t>55,80%|Pós-Fixada</x:t>
@@ -88,10 +88,10 @@
     <x:t>R$ 2.320.442,51</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.333.723,55</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.330.735,32</x:t>
+    <x:t>R$ 2.336.799,18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.333.118,93</x:t>
   </x:si>
   <x:si>
     <x:t>07/08/2026</x:t>
@@ -103,10 +103,10 @@
     <x:t>R$ 1.999.048,84</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.009.607,95</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.007.232,15</x:t>
+    <x:t>R$ 2.012.256,43</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.009.284,72</x:t>
   </x:si>
   <x:si>
     <x:t>17/08/2026</x:t>
@@ -121,16 +121,16 @@
     <x:t>R$ 1.999.998,41</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.005.273,50</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.004.086,60</x:t>
+    <x:t>R$ 2.007.916,27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.006.134,75</x:t>
   </x:si>
   <x:si>
     <x:t>44,1%|Fundos de Investimento</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 5.010.218,86</x:t>
+    <x:t>R$ 5.018.017,13</x:t>
   </x:si>
   <x:si>
     <x:t>44,10%|Fundos de Renda Fixa Pós-Fixado</x:t>
@@ -151,10 +151,10 @@
     <x:t>Safra DI Master FIRF Referenciado DI LP</x:t>
   </x:si>
   <x:si>
-    <x:t>24/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 272,16</x:t>
+    <x:t>27/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 272,58</x:t>
   </x:si>
   <x:si>
     <x:t>7.363,69</x:t>
@@ -163,28 +163,28 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.004.067,02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.000.630,40</x:t>
+    <x:t>R$ 2.007.193,49</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.001.672,49</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
   </x:si>
   <x:si>
-    <x:t>25/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.441,09</x:t>
+    <x:t>28/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.443,31</x:t>
   </x:si>
   <x:si>
     <x:t>1.390,64</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.004.043,72</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.000.626,78</x:t>
+    <x:t>R$ 2.007.130,26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.001.657,79</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
@@ -196,10 +196,10 @@
     <x:t>680.719,86</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.002.108,12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.000.326,76</x:t>
+    <x:t>R$ 1.003.693,38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.000.858,71</x:t>
   </x:si>
   <x:si>
     <x:t>R$ 382,83</x:t>
@@ -840,10 +840,10 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>11359206.6880217</x:v>
+        <x:v>11375371.8430789</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>11358823.8580217</x:v>
+        <x:v>11374989.0130789</x:v>
       </x:c>
       <x:c r="C4" s="7">
         <x:v>382.83</x:v>

--- a/data/positions/Posição Consolidada - 5166121.xlsx
+++ b/data/positions/Posição Consolidada - 5166121.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 5166121 | 28/08/2026, 09:33</x:t>
+    <x:t>Conta: 5166121 | 31/08/2026, 17:49</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,13 +34,13 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>55,9%|Operações Compromissadas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 6.356.971,88</x:t>
-  </x:si>
-  <x:si>
-    <x:t>55,80%|Pós-Fixada</x:t>
+    <x:t>43,4%|Operações Compromissadas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 3.852.417,96</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43,40%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -70,70 +70,67 @@
     <x:t>Valor líquido</x:t>
   </x:si>
   <x:si>
-    <x:t>06/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04/09/2026</x:t>
+    <x:t>17/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18/09/2026</x:t>
   </x:si>
   <x:si>
     <x:t>85,00% CDI</x:t>
   </x:si>
   <x:si>
-    <x:t>2.231,00</x:t>
+    <x:t>536.588,00</x:t>
   </x:si>
   <x:si>
     <x:t>0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.320.442,51</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.336.799,18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.333.118,93</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.162.237,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.999.048,84</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.012.256,43</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.009.284,72</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.265.821,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.999.998,41</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.007.916,27</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.006.134,75</x:t>
-  </x:si>
-  <x:si>
-    <x:t>44,1%|Fundos de Investimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.018.017,13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>44,10%|Fundos de Renda Fixa Pós-Fixado</x:t>
+    <x:t>R$ 847.809,56</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 851.539,74</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 850.700,45</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.411,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.000.000,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.000.878,22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.000.680,62</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01/10/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2.961,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.000.000,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>56,6%|Fundos de Investimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.021.620,37</x:t>
+  </x:si>
+  <x:si>
+    <x:t>56,50%|Fundos de Renda Fixa Pós-Fixado</x:t>
   </x:si>
   <x:si>
     <x:t>Data cota</x:t>
@@ -151,10 +148,7 @@
     <x:t>Safra DI Master FIRF Referenciado DI LP</x:t>
   </x:si>
   <x:si>
-    <x:t>27/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 272,58</x:t>
+    <x:t>R$ 272,86</x:t>
   </x:si>
   <x:si>
     <x:t>7.363,69</x:t>
@@ -163,46 +157,43 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.007.193,49</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.001.672,49</x:t>
+    <x:t>R$ 2.009.272,14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.003.161,81</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
   </x:si>
   <x:si>
-    <x:t>28/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.443,31</x:t>
+    <x:t>R$ 1.444,03</x:t>
   </x:si>
   <x:si>
     <x:t>1.390,64</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.007.130,26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.001.657,79</x:t>
+    <x:t>R$ 2.008.129,47</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.002.520,14</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1,47</x:t>
+    <x:t>R$ 1,48</x:t>
   </x:si>
   <x:si>
     <x:t>680.719,86</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.003.693,38</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.000.858,71</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 382,83</x:t>
+    <x:t>R$ 1.004.218,76</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.001.307,82</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 384,14</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -232,7 +223,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>382,83</x:t>
+    <x:t>384,14</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -840,13 +831,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>11375371.8430789</x:v>
+        <x:v>8874422.4677918</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>11374989.0130789</x:v>
+        <x:v>8874038.3277918</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>382.83</x:v>
+        <x:v>384.14</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
@@ -984,54 +975,54 @@
       </x:c>
       <x:c r="C11" s="12"/>
       <x:c r="D11" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E11" s="12" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="F11" s="12" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G11" s="12" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="H11" s="12" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="I11" s="12" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="J11" s="12" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="K11" s="3"/>
     </x:row>
     <x:row r="12" spans="1:11" ht="30" customHeight="1">
       <x:c r="A12" s="13"/>
       <x:c r="B12" s="13" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C12" s="13"/>
       <x:c r="D12" s="13" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E12" s="13" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="F12" s="13" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G12" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="H12" s="13" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="I12" s="13" t="s">
         <x:v>35</x:v>
       </x:c>
       <x:c r="J12" s="13" t="s">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="K12" s="3"/>
     </x:row>
@@ -1050,7 +1041,7 @@
     </x:row>
     <x:row r="14" spans="1:11" ht="45" customHeight="1">
       <x:c r="A14" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B14" s="9"/>
       <x:c r="C14" s="9"/>
@@ -1058,7 +1049,7 @@
       <x:c r="E14" s="9"/>
       <x:c r="F14" s="9"/>
       <x:c r="G14" s="10" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="H14" s="3"/>
       <x:c r="I14" s="3"/>
@@ -1080,19 +1071,19 @@
     </x:row>
     <x:row r="16" spans="1:11" ht="35.1" customHeight="1">
       <x:c r="A16" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B16" s="11" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="B16" s="11" t="s">
+      <x:c r="C16" s="11" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C16" s="11" t="s">
+      <x:c r="D16" s="11" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="D16" s="11" t="s">
+      <x:c r="E16" s="11" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="E16" s="11" t="s">
-        <x:v>43</x:v>
       </x:c>
       <x:c r="F16" s="11" t="s">
         <x:v>16</x:v>
@@ -1107,25 +1098,25 @@
     </x:row>
     <x:row r="17" spans="1:11" ht="30" customHeight="1">
       <x:c r="A17" s="12" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B17" s="12" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C17" s="12" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="B17" s="12" t="s">
+      <x:c r="D17" s="12" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="C17" s="12" t="s">
+      <x:c r="E17" s="12" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="D17" s="12" t="s">
+      <x:c r="F17" s="12" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="E17" s="12" t="s">
+      <x:c r="G17" s="12" t="s">
         <x:v>48</x:v>
-      </x:c>
-      <x:c r="F17" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="G17" s="12" t="s">
-        <x:v>50</x:v>
       </x:c>
       <x:c r="H17" s="3"/>
       <x:c r="I17" s="3"/>
@@ -1134,25 +1125,25 @@
     </x:row>
     <x:row r="18" spans="1:11" ht="30" customHeight="1">
       <x:c r="A18" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B18" s="12" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C18" s="12" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D18" s="12" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="B18" s="12" t="s">
+      <x:c r="E18" s="12" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="F18" s="12" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C18" s="12" t="s">
+      <x:c r="G18" s="12" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="D18" s="12" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E18" s="12" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="F18" s="12" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="G18" s="12" t="s">
-        <x:v>56</x:v>
       </x:c>
       <x:c r="H18" s="3"/>
       <x:c r="I18" s="3"/>
@@ -1161,25 +1152,25 @@
     </x:row>
     <x:row r="19" spans="1:11" ht="30" customHeight="1">
       <x:c r="A19" s="13" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B19" s="13" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C19" s="13" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="D19" s="13" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="E19" s="13" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="F19" s="13" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="B19" s="13" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C19" s="13" t="s">
+      <x:c r="G19" s="13" t="s">
         <x:v>58</x:v>
-      </x:c>
-      <x:c r="D19" s="13" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="E19" s="13" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="F19" s="13" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="G19" s="13" t="s">
-        <x:v>61</x:v>
       </x:c>
       <x:c r="H19" s="3"/>
       <x:c r="I19" s="3"/>
@@ -1213,7 +1204,7 @@
       <x:c r="I21" s="9"/>
       <x:c r="J21" s="9"/>
       <x:c r="K21" s="10" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:11">
@@ -1237,66 +1228,66 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C23" s="11" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D23" s="11" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E23" s="11" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F23" s="11" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="D23" s="11" t="s">
+      <x:c r="G23" s="11" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="E23" s="11" t="s">
+      <x:c r="H23" s="11" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="F23" s="11" t="s">
+      <x:c r="I23" s="11" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="G23" s="11" t="s">
+      <x:c r="J23" s="11" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="H23" s="11" t="s">
+      <x:c r="K23" s="11" t="s">
         <x:v>68</x:v>
-      </x:c>
-      <x:c r="I23" s="11" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="J23" s="11" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="K23" s="11" t="s">
-        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:11" ht="30" customHeight="1">
       <x:c r="A24" s="13" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B24" s="13" t="s">
-        <x:v>73</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C24" s="13" t="s">
-        <x:v>73</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D24" s="13" t="s">
-        <x:v>73</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E24" s="13" t="s">
-        <x:v>73</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F24" s="13" t="s">
-        <x:v>73</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="G24" s="13" t="s">
-        <x:v>73</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="H24" s="13" t="s">
-        <x:v>73</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="I24" s="13" t="s">
-        <x:v>73</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="J24" s="13" t="s">
-        <x:v>73</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="K24" s="13" t="s">
-        <x:v>73</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/data/positions/Posição Consolidada - 5166121.xlsx
+++ b/data/positions/Posição Consolidada - 5166121.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 5166121 | 31/08/2026, 17:49</x:t>
+    <x:t>Conta: 5166121 | 01/09/2026, 15:59</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>43,4%|Operações Compromissadas</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 3.852.417,96</x:t>
+    <x:t>R$ 3.854.109,59</x:t>
   </x:si>
   <x:si>
     <x:t>43,40%|Pós-Fixada</x:t>
@@ -88,10 +88,10 @@
     <x:t>R$ 847.809,56</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 851.539,74</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 850.700,45</x:t>
+    <x:t>R$ 851.913,66</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 850.990,24</x:t>
   </x:si>
   <x:si>
     <x:t>28/08/2026</x:t>
@@ -106,10 +106,10 @@
     <x:t>R$ 2.000.000,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.000.878,22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.000.680,62</x:t>
+    <x:t>R$ 2.001.756,83</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.001.361,54</x:t>
   </x:si>
   <x:si>
     <x:t>31/08/2026</x:t>
@@ -124,10 +124,16 @@
     <x:t>R$ 1.000.000,00</x:t>
   </x:si>
   <x:si>
+    <x:t>R$ 1.000.439,11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.000.340,31</x:t>
+  </x:si>
+  <x:si>
     <x:t>56,6%|Fundos de Investimento</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 5.021.620,37</x:t>
+    <x:t>R$ 5.024.215,32</x:t>
   </x:si>
   <x:si>
     <x:t>56,50%|Fundos de Renda Fixa Pós-Fixado</x:t>
@@ -148,7 +154,10 @@
     <x:t>Safra DI Master FIRF Referenciado DI LP</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 272,86</x:t>
+    <x:t>01/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 273,00</x:t>
   </x:si>
   <x:si>
     <x:t>7.363,69</x:t>
@@ -157,25 +166,25 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.009.272,14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.003.161,81</x:t>
+    <x:t>R$ 2.010.298,02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.003.751,06</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.444,03</x:t>
+    <x:t>R$ 1.444,78</x:t>
   </x:si>
   <x:si>
     <x:t>1.390,64</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.008.129,47</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.002.520,14</x:t>
+    <x:t>R$ 2.009.167,30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.003.126,05</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
@@ -187,10 +196,10 @@
     <x:t>680.719,86</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.004.218,76</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.001.307,82</x:t>
+    <x:t>R$ 1.004.750,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.001.619,75</x:t>
   </x:si>
   <x:si>
     <x:t>R$ 384,14</x:t>
@@ -831,10 +840,10 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>8874422.4677918</x:v>
+        <x:v>8878709.05476101</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>8874038.3277918</x:v>
+        <x:v>8878324.91476101</x:v>
       </x:c>
       <x:c r="C4" s="7">
         <x:v>384.14</x:v>
@@ -1019,10 +1028,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="I12" s="13" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="J12" s="13" t="s">
-        <x:v>35</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="K12" s="3"/>
     </x:row>
@@ -1041,7 +1050,7 @@
     </x:row>
     <x:row r="14" spans="1:11" ht="45" customHeight="1">
       <x:c r="A14" s="8" t="s">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B14" s="9"/>
       <x:c r="C14" s="9"/>
@@ -1049,7 +1058,7 @@
       <x:c r="E14" s="9"/>
       <x:c r="F14" s="9"/>
       <x:c r="G14" s="10" t="s">
-        <x:v>37</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H14" s="3"/>
       <x:c r="I14" s="3"/>
@@ -1071,19 +1080,19 @@
     </x:row>
     <x:row r="16" spans="1:11" ht="35.1" customHeight="1">
       <x:c r="A16" s="11" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B16" s="11" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C16" s="11" t="s">
-        <x:v>40</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D16" s="11" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E16" s="11" t="s">
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F16" s="11" t="s">
         <x:v>16</x:v>
@@ -1098,25 +1107,25 @@
     </x:row>
     <x:row r="17" spans="1:11" ht="30" customHeight="1">
       <x:c r="A17" s="12" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B17" s="12" t="s">
-        <x:v>32</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C17" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D17" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E17" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F17" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G17" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H17" s="3"/>
       <x:c r="I17" s="3"/>
@@ -1125,25 +1134,25 @@
     </x:row>
     <x:row r="18" spans="1:11" ht="30" customHeight="1">
       <x:c r="A18" s="12" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B18" s="12" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C18" s="12" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D18" s="12" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E18" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="B18" s="12" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C18" s="12" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="D18" s="12" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="E18" s="12" t="s">
-        <x:v>46</x:v>
-      </x:c>
       <x:c r="F18" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G18" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H18" s="3"/>
       <x:c r="I18" s="3"/>
@@ -1152,25 +1161,25 @@
     </x:row>
     <x:row r="19" spans="1:11" ht="30" customHeight="1">
       <x:c r="A19" s="13" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B19" s="13" t="s">
-        <x:v>32</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C19" s="13" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D19" s="13" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E19" s="13" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F19" s="13" t="s">
-        <x:v>57</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G19" s="13" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="H19" s="3"/>
       <x:c r="I19" s="3"/>
@@ -1204,7 +1213,7 @@
       <x:c r="I21" s="9"/>
       <x:c r="J21" s="9"/>
       <x:c r="K21" s="10" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:11">
@@ -1228,66 +1237,66 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C23" s="11" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D23" s="11" t="s">
-        <x:v>61</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E23" s="11" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F23" s="11" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="G23" s="11" t="s">
-        <x:v>64</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H23" s="11" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="I23" s="11" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="J23" s="11" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="K23" s="11" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:11" ht="30" customHeight="1">
       <x:c r="A24" s="13" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B24" s="13" t="s">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C24" s="13" t="s">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D24" s="13" t="s">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E24" s="13" t="s">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="F24" s="13" t="s">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="G24" s="13" t="s">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="H24" s="13" t="s">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="I24" s="13" t="s">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="J24" s="13" t="s">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="K24" s="13" t="s">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/data/positions/Posição Consolidada - 5166121.xlsx
+++ b/data/positions/Posição Consolidada - 5166121.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 5166121 | 01/09/2026, 15:59</x:t>
+    <x:t>Conta: 5166121 | 04/09/2026, 14:14</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,13 +34,13 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>43,4%|Operações Compromissadas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 3.854.109,59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43,40%|Pós-Fixada</x:t>
+    <x:t>41,4%|Operações Compromissadas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 3.558.672,11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>41,40%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -79,19 +79,19 @@
     <x:t>85,00% CDI</x:t>
   </x:si>
   <x:si>
-    <x:t>536.588,00</x:t>
+    <x:t>347.553,00</x:t>
   </x:si>
   <x:si>
     <x:t>0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 847.809,56</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 851.913,66</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 850.990,24</x:t>
+    <x:t>R$ 549.134,08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 552.519,55</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 551.757,82</x:t>
   </x:si>
   <x:si>
     <x:t>28/08/2026</x:t>
@@ -106,10 +106,10 @@
     <x:t>R$ 2.000.000,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.001.756,83</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.001.361,54</x:t>
+    <x:t>R$ 2.004.394,96</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.003.406,09</x:t>
   </x:si>
   <x:si>
     <x:t>31/08/2026</x:t>
@@ -124,19 +124,19 @@
     <x:t>R$ 1.000.000,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.000.439,11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.000.340,31</x:t>
-  </x:si>
-  <x:si>
-    <x:t>56,6%|Fundos de Investimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.024.215,32</x:t>
-  </x:si>
-  <x:si>
-    <x:t>56,50%|Fundos de Renda Fixa Pós-Fixado</x:t>
+    <x:t>R$ 1.001.757,60</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.001.362,14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>58,6%|Fundos de Investimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.032.062,97</x:t>
+  </x:si>
+  <x:si>
+    <x:t>58,50%|Fundos de Renda Fixa Pós-Fixado</x:t>
   </x:si>
   <x:si>
     <x:t>Data cota</x:t>
@@ -154,10 +154,10 @@
     <x:t>Safra DI Master FIRF Referenciado DI LP</x:t>
   </x:si>
   <x:si>
-    <x:t>01/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 273,00</x:t>
+    <x:t>04/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 273,42</x:t>
   </x:si>
   <x:si>
     <x:t>7.363,69</x:t>
@@ -166,25 +166,25 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.010.298,02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.003.751,06</x:t>
+    <x:t>R$ 2.013.361,41</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.005.902,41</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.444,78</x:t>
+    <x:t>R$ 1.447,05</x:t>
   </x:si>
   <x:si>
     <x:t>1.390,64</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.009.167,30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.003.126,05</x:t>
+    <x:t>R$ 2.012.334,24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.005.161,88</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
@@ -196,13 +196,13 @@
     <x:t>680.719,86</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.004.750,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.001.619,75</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 384,14</x:t>
+    <x:t>R$ 1.006.367,32</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.002.664,72</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 384,47</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -232,7 +232,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>384,14</x:t>
+    <x:t>384,47</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -840,13 +840,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>8878709.05476101</x:v>
+        <x:v>8591119.54791837</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>8878324.91476101</x:v>
+        <x:v>8590735.07791837</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>384.14</x:v>
+        <x:v>384.47</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>

--- a/data/positions/Posição Consolidada - 5166121.xlsx
+++ b/data/positions/Posição Consolidada - 5166121.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 5166121 | 04/09/2026, 14:14</x:t>
+    <x:t>Conta: 5166121 | 10/09/2026, 14:05</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,13 +34,13 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>41,4%|Operações Compromissadas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 3.558.672,11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>41,40%|Pós-Fixada</x:t>
+    <x:t>33,7%|Operações Compromissadas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.561.441,50</x:t>
+  </x:si>
+  <x:si>
+    <x:t>33,60%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -70,46 +70,28 @@
     <x:t>Valor líquido</x:t>
   </x:si>
   <x:si>
-    <x:t>17/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18/09/2026</x:t>
+    <x:t>28/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29/09/2026</x:t>
   </x:si>
   <x:si>
     <x:t>85,00% CDI</x:t>
   </x:si>
   <x:si>
-    <x:t>347.553,00</x:t>
+    <x:t>1.097,00</x:t>
   </x:si>
   <x:si>
     <x:t>0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 549.134,08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 552.519,55</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 551.757,82</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.411,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.000.000,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.004.394,96</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.003.406,09</x:t>
+    <x:t>R$ 1.554.925,58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.560.396,25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.559.165,35</x:t>
   </x:si>
   <x:si>
     <x:t>31/08/2026</x:t>
@@ -118,25 +100,25 @@
     <x:t>01/10/2026</x:t>
   </x:si>
   <x:si>
-    <x:t>2.961,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.000.000,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.001.757,60</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.001.362,14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>58,6%|Fundos de Investimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.032.062,97</x:t>
-  </x:si>
-  <x:si>
-    <x:t>58,50%|Fundos de Renda Fixa Pós-Fixado</x:t>
+    <x:t>2.955,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 997.973,66</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.001.045,24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.000.354,13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>66,3%|Fundos de Investimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.039.668,67</x:t>
+  </x:si>
+  <x:si>
+    <x:t>66,20%|Fundos de Renda Fixa Pós-Fixado</x:t>
   </x:si>
   <x:si>
     <x:t>Data cota</x:t>
@@ -154,10 +136,10 @@
     <x:t>Safra DI Master FIRF Referenciado DI LP</x:t>
   </x:si>
   <x:si>
-    <x:t>04/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 273,42</x:t>
+    <x:t>10/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 273,83</x:t>
   </x:si>
   <x:si>
     <x:t>7.363,69</x:t>
@@ -166,25 +148,25 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.013.361,41</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.005.902,41</x:t>
+    <x:t>R$ 2.016.406,29</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.009.790,46</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.447,05</x:t>
+    <x:t>R$ 1.449,20</x:t>
   </x:si>
   <x:si>
     <x:t>1.390,64</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.012.334,24</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.005.161,88</x:t>
+    <x:t>R$ 2.015.322,74</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.008.787,60</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
@@ -196,13 +178,16 @@
     <x:t>680.719,86</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.006.367,32</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.002.664,72</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 384,47</x:t>
+    <x:t>R$ 1.007.939,64</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.004.553,39</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0,01%|Saldo projetado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 565,56</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -232,7 +217,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>384,47</x:t>
+    <x:t>565,56</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -780,7 +765,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K24"/>
+  <x:dimension ref="A1:K23"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="38.282054" style="0" customWidth="1"/>
@@ -840,13 +825,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>8591119.54791837</x:v>
+        <x:v>7601675.72685375</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>8590735.07791837</x:v>
+        <x:v>7601110.16685375</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>384.47</x:v>
+        <x:v>565.56</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
@@ -978,127 +963,125 @@
       <x:c r="K10" s="3"/>
     </x:row>
     <x:row r="11" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A11" s="12"/>
-      <x:c r="B11" s="12" t="s">
+      <x:c r="A11" s="13"/>
+      <x:c r="B11" s="13" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C11" s="12"/>
-      <x:c r="D11" s="12" t="s">
+      <x:c r="C11" s="13"/>
+      <x:c r="D11" s="13" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="E11" s="12" t="s">
+      <x:c r="E11" s="13" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="F11" s="12" t="s">
+      <x:c r="F11" s="13" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="G11" s="12" t="s">
+      <x:c r="G11" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="H11" s="12" t="s">
+      <x:c r="H11" s="13" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="I11" s="12" t="s">
+      <x:c r="I11" s="13" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="J11" s="12" t="s">
+      <x:c r="J11" s="13" t="s">
         <x:v>31</x:v>
       </x:c>
       <x:c r="K11" s="3"/>
     </x:row>
-    <x:row r="12" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A12" s="13"/>
-      <x:c r="B12" s="13" t="s">
+    <x:row r="12" spans="1:11">
+      <x:c r="A12" s="4"/>
+      <x:c r="B12" s="4"/>
+      <x:c r="C12" s="4"/>
+      <x:c r="D12" s="4"/>
+      <x:c r="E12" s="4"/>
+      <x:c r="F12" s="4"/>
+      <x:c r="G12" s="4"/>
+      <x:c r="H12" s="4"/>
+      <x:c r="I12" s="4"/>
+      <x:c r="J12" s="4"/>
+      <x:c r="K12" s="4"/>
+    </x:row>
+    <x:row r="13" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A13" s="8" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C12" s="13"/>
-      <x:c r="D12" s="13" t="s">
+      <x:c r="B13" s="9"/>
+      <x:c r="C13" s="9"/>
+      <x:c r="D13" s="9"/>
+      <x:c r="E13" s="9"/>
+      <x:c r="F13" s="9"/>
+      <x:c r="G13" s="10" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="E12" s="13" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F12" s="13" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="G12" s="13" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H12" s="13" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="I12" s="13" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="J12" s="13" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="K12" s="3"/>
-    </x:row>
-    <x:row r="13" spans="1:11">
-      <x:c r="A13" s="4"/>
-      <x:c r="B13" s="4"/>
-      <x:c r="C13" s="4"/>
-      <x:c r="D13" s="4"/>
-      <x:c r="E13" s="4"/>
-      <x:c r="F13" s="4"/>
-      <x:c r="G13" s="4"/>
-      <x:c r="H13" s="4"/>
-      <x:c r="I13" s="4"/>
-      <x:c r="J13" s="4"/>
-      <x:c r="K13" s="4"/>
-    </x:row>
-    <x:row r="14" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A14" s="8" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="B14" s="9"/>
-      <x:c r="C14" s="9"/>
-      <x:c r="D14" s="9"/>
-      <x:c r="E14" s="9"/>
-      <x:c r="F14" s="9"/>
-      <x:c r="G14" s="10" t="s">
-        <x:v>39</x:v>
-      </x:c>
+      <x:c r="H13" s="3"/>
+      <x:c r="I13" s="3"/>
+      <x:c r="J13" s="3"/>
+      <x:c r="K13" s="3"/>
+    </x:row>
+    <x:row r="14" spans="1:11">
+      <x:c r="A14" s="4"/>
+      <x:c r="B14" s="4"/>
+      <x:c r="C14" s="4"/>
+      <x:c r="D14" s="4"/>
+      <x:c r="E14" s="4"/>
+      <x:c r="F14" s="4"/>
+      <x:c r="G14" s="4"/>
       <x:c r="H14" s="3"/>
       <x:c r="I14" s="3"/>
       <x:c r="J14" s="3"/>
       <x:c r="K14" s="3"/>
     </x:row>
-    <x:row r="15" spans="1:11">
-      <x:c r="A15" s="4"/>
-      <x:c r="B15" s="4"/>
-      <x:c r="C15" s="4"/>
-      <x:c r="D15" s="4"/>
-      <x:c r="E15" s="4"/>
-      <x:c r="F15" s="4"/>
-      <x:c r="G15" s="4"/>
+    <x:row r="15" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A15" s="11" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B15" s="11" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C15" s="11" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D15" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E15" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F15" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G15" s="11" t="s">
+        <x:v>17</x:v>
+      </x:c>
       <x:c r="H15" s="3"/>
       <x:c r="I15" s="3"/>
       <x:c r="J15" s="3"/>
       <x:c r="K15" s="3"/>
     </x:row>
-    <x:row r="16" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A16" s="11" t="s">
+    <x:row r="16" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A16" s="12" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B16" s="12" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="B16" s="11" t="s">
+      <x:c r="C16" s="12" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="C16" s="11" t="s">
+      <x:c r="D16" s="12" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="D16" s="11" t="s">
+      <x:c r="E16" s="12" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="E16" s="11" t="s">
+      <x:c r="F16" s="12" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="F16" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G16" s="11" t="s">
-        <x:v>17</x:v>
+      <x:c r="G16" s="12" t="s">
+        <x:v>45</x:v>
       </x:c>
       <x:c r="H16" s="3"/>
       <x:c r="I16" s="3"/>
@@ -1107,10 +1090,10 @@
     </x:row>
     <x:row r="17" spans="1:11" ht="30" customHeight="1">
       <x:c r="A17" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B17" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C17" s="12" t="s">
         <x:v>47</x:v>
@@ -1119,13 +1102,13 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="E17" s="12" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F17" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="F17" s="12" t="s">
+      <x:c r="G17" s="12" t="s">
         <x:v>50</x:v>
-      </x:c>
-      <x:c r="G17" s="12" t="s">
-        <x:v>51</x:v>
       </x:c>
       <x:c r="H17" s="3"/>
       <x:c r="I17" s="3"/>
@@ -1133,170 +1116,143 @@
       <x:c r="K17" s="3"/>
     </x:row>
     <x:row r="18" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A18" s="12" t="s">
+      <x:c r="A18" s="13" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B18" s="13" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C18" s="13" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="B18" s="12" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C18" s="12" t="s">
+      <x:c r="D18" s="13" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="D18" s="12" t="s">
+      <x:c r="E18" s="13" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F18" s="13" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E18" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="F18" s="12" t="s">
+      <x:c r="G18" s="13" t="s">
         <x:v>55</x:v>
-      </x:c>
-      <x:c r="G18" s="12" t="s">
-        <x:v>56</x:v>
       </x:c>
       <x:c r="H18" s="3"/>
       <x:c r="I18" s="3"/>
       <x:c r="J18" s="3"/>
       <x:c r="K18" s="3"/>
     </x:row>
-    <x:row r="19" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A19" s="13" t="s">
+    <x:row r="19" spans="1:11">
+      <x:c r="A19" s="4"/>
+      <x:c r="B19" s="4"/>
+      <x:c r="C19" s="4"/>
+      <x:c r="D19" s="4"/>
+      <x:c r="E19" s="4"/>
+      <x:c r="F19" s="4"/>
+      <x:c r="G19" s="4"/>
+      <x:c r="H19" s="4"/>
+      <x:c r="I19" s="4"/>
+      <x:c r="J19" s="4"/>
+      <x:c r="K19" s="4"/>
+    </x:row>
+    <x:row r="20" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A20" s="8" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B20" s="9"/>
+      <x:c r="C20" s="9"/>
+      <x:c r="D20" s="9"/>
+      <x:c r="E20" s="9"/>
+      <x:c r="F20" s="9"/>
+      <x:c r="G20" s="9"/>
+      <x:c r="H20" s="9"/>
+      <x:c r="I20" s="9"/>
+      <x:c r="J20" s="9"/>
+      <x:c r="K20" s="10" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="B19" s="13" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C19" s="13" t="s">
+    </x:row>
+    <x:row r="21" spans="1:11">
+      <x:c r="A21" s="4"/>
+      <x:c r="B21" s="4"/>
+      <x:c r="C21" s="4"/>
+      <x:c r="D21" s="4"/>
+      <x:c r="E21" s="4"/>
+      <x:c r="F21" s="4"/>
+      <x:c r="G21" s="4"/>
+      <x:c r="H21" s="4"/>
+      <x:c r="I21" s="4"/>
+      <x:c r="J21" s="4"/>
+      <x:c r="K21" s="4"/>
+    </x:row>
+    <x:row r="22" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A22" s="11" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B22" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C22" s="11" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="D19" s="13" t="s">
+      <x:c r="D22" s="11" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="E19" s="13" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="F19" s="13" t="s">
+      <x:c r="E22" s="11" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="G19" s="13" t="s">
+      <x:c r="F22" s="11" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="H19" s="3"/>
-      <x:c r="I19" s="3"/>
-      <x:c r="J19" s="3"/>
-      <x:c r="K19" s="3"/>
-    </x:row>
-    <x:row r="20" spans="1:11">
-      <x:c r="A20" s="4"/>
-      <x:c r="B20" s="4"/>
-      <x:c r="C20" s="4"/>
-      <x:c r="D20" s="4"/>
-      <x:c r="E20" s="4"/>
-      <x:c r="F20" s="4"/>
-      <x:c r="G20" s="4"/>
-      <x:c r="H20" s="4"/>
-      <x:c r="I20" s="4"/>
-      <x:c r="J20" s="4"/>
-      <x:c r="K20" s="4"/>
-    </x:row>
-    <x:row r="21" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A21" s="8" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B21" s="9"/>
-      <x:c r="C21" s="9"/>
-      <x:c r="D21" s="9"/>
-      <x:c r="E21" s="9"/>
-      <x:c r="F21" s="9"/>
-      <x:c r="G21" s="9"/>
-      <x:c r="H21" s="9"/>
-      <x:c r="I21" s="9"/>
-      <x:c r="J21" s="9"/>
-      <x:c r="K21" s="10" t="s">
+      <x:c r="G22" s="11" t="s">
         <x:v>62</x:v>
       </x:c>
-    </x:row>
-    <x:row r="22" spans="1:11">
-      <x:c r="A22" s="4"/>
-      <x:c r="B22" s="4"/>
-      <x:c r="C22" s="4"/>
-      <x:c r="D22" s="4"/>
-      <x:c r="E22" s="4"/>
-      <x:c r="F22" s="4"/>
-      <x:c r="G22" s="4"/>
-      <x:c r="H22" s="4"/>
-      <x:c r="I22" s="4"/>
-      <x:c r="J22" s="4"/>
-      <x:c r="K22" s="4"/>
-    </x:row>
-    <x:row r="23" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A23" s="11" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B23" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C23" s="11" t="s">
+      <x:c r="H22" s="11" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="D23" s="11" t="s">
+      <x:c r="I22" s="11" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="E23" s="11" t="s">
+      <x:c r="J22" s="11" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="F23" s="11" t="s">
+      <x:c r="K22" s="11" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="G23" s="11" t="s">
+    </x:row>
+    <x:row r="23" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A23" s="13" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="H23" s="11" t="s">
+      <x:c r="B23" s="13" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="I23" s="11" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="J23" s="11" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="K23" s="11" t="s">
-        <x:v>71</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A24" s="13" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="B24" s="13" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C24" s="13" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="D24" s="13" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="E24" s="13" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="F24" s="13" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="G24" s="13" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="H24" s="13" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="I24" s="13" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="J24" s="13" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="K24" s="13" t="s">
-        <x:v>73</x:v>
+      <x:c r="C23" s="13" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D23" s="13" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="E23" s="13" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="F23" s="13" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="G23" s="13" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="H23" s="13" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="I23" s="13" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="J23" s="13" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="K23" s="13" t="s">
+        <x:v>68</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1304,8 +1260,8 @@
     <x:mergeCell ref="A1:E1"/>
     <x:mergeCell ref="F1:G1"/>
     <x:mergeCell ref="A7:F7"/>
-    <x:mergeCell ref="A14:F14"/>
-    <x:mergeCell ref="A21:J21"/>
+    <x:mergeCell ref="A13:F13"/>
+    <x:mergeCell ref="A20:J20"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/data/positions/Posição Consolidada - 5166121.xlsx
+++ b/data/positions/Posição Consolidada - 5166121.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 5166121 | 10/09/2026, 14:05</x:t>
+    <x:t>Conta: 5166121 | 16/09/2026, 08:42</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,13 +34,13 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>33,7%|Operações Compromissadas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.561.441,50</x:t>
-  </x:si>
-  <x:si>
-    <x:t>33,60%|Pós-Fixada</x:t>
+    <x:t>42,4%|Operações Compromissadas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 3.713.608,72</x:t>
+  </x:si>
+  <x:si>
+    <x:t>42,30%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -79,19 +79,19 @@
     <x:t>85,00% CDI</x:t>
   </x:si>
   <x:si>
-    <x:t>1.097,00</x:t>
+    <x:t>850,00</x:t>
   </x:si>
   <x:si>
     <x:t>0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.554.925,58</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.560.396,25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.559.165,35</x:t>
+    <x:t>R$ 1.204.819,28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.211.183,21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.209.751,33</x:t>
   </x:si>
   <x:si>
     <x:t>31/08/2026</x:t>
@@ -100,25 +100,43 @@
     <x:t>01/10/2026</x:t>
   </x:si>
   <x:si>
-    <x:t>2.955,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 997.973,66</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.001.045,24</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.000.354,13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>66,3%|Fundos de Investimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.039.668,67</x:t>
-  </x:si>
-  <x:si>
-    <x:t>66,20%|Fundos de Renda Fixa Pós-Fixado</x:t>
+    <x:t>2.950,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 996.285,04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.001.107,88</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.000.022,74</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14/10/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>882.352,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.500.000,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.501.317,62</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.501.021,15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>57,6%|Fundos de Investimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.048.539,86</x:t>
+  </x:si>
+  <x:si>
+    <x:t>57,50%|Fundos de Renda Fixa Pós-Fixado</x:t>
   </x:si>
   <x:si>
     <x:t>Data cota</x:t>
@@ -136,10 +154,10 @@
     <x:t>Safra DI Master FIRF Referenciado DI LP</x:t>
   </x:si>
   <x:si>
-    <x:t>10/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 273,83</x:t>
+    <x:t>15/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 274,26</x:t>
   </x:si>
   <x:si>
     <x:t>7.363,69</x:t>
@@ -148,25 +166,28 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.016.406,29</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.009.790,46</x:t>
+    <x:t>R$ 2.019.561,80</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.014.250,78</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.449,20</x:t>
+    <x:t>16/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.452,18</x:t>
   </x:si>
   <x:si>
     <x:t>1.390,64</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.015.322,74</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.008.787,60</x:t>
+    <x:t>R$ 2.019.467,79</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.014.182,29</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
@@ -178,16 +199,16 @@
     <x:t>680.719,86</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.007.939,64</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.004.553,39</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0,01%|Saldo projetado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 565,56</x:t>
+    <x:t>R$ 1.009.510,27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.006.633,42</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0,04%|Saldo projetado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 3.089,05</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -217,7 +238,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>565,56</x:t>
+    <x:t>3089,05</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -765,7 +786,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K23"/>
+  <x:dimension ref="A1:K24"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="38.282054" style="0" customWidth="1"/>
@@ -825,13 +846,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>7601675.72685375</x:v>
+        <x:v>8765237.62675774</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>7601110.16685375</x:v>
+        <x:v>8762148.57675774</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>565.56</x:v>
+        <x:v>3089.05</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
@@ -963,125 +984,127 @@
       <x:c r="K10" s="3"/>
     </x:row>
     <x:row r="11" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A11" s="13"/>
-      <x:c r="B11" s="13" t="s">
+      <x:c r="A11" s="12"/>
+      <x:c r="B11" s="12" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C11" s="13"/>
-      <x:c r="D11" s="13" t="s">
+      <x:c r="C11" s="12"/>
+      <x:c r="D11" s="12" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="E11" s="13" t="s">
+      <x:c r="E11" s="12" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="F11" s="13" t="s">
+      <x:c r="F11" s="12" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="G11" s="13" t="s">
+      <x:c r="G11" s="12" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="H11" s="13" t="s">
+      <x:c r="H11" s="12" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="I11" s="13" t="s">
+      <x:c r="I11" s="12" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="J11" s="13" t="s">
+      <x:c r="J11" s="12" t="s">
         <x:v>31</x:v>
       </x:c>
       <x:c r="K11" s="3"/>
     </x:row>
-    <x:row r="12" spans="1:11">
-      <x:c r="A12" s="4"/>
-      <x:c r="B12" s="4"/>
-      <x:c r="C12" s="4"/>
-      <x:c r="D12" s="4"/>
-      <x:c r="E12" s="4"/>
-      <x:c r="F12" s="4"/>
-      <x:c r="G12" s="4"/>
-      <x:c r="H12" s="4"/>
-      <x:c r="I12" s="4"/>
-      <x:c r="J12" s="4"/>
-      <x:c r="K12" s="4"/>
-    </x:row>
-    <x:row r="13" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A13" s="8" t="s">
+    <x:row r="12" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A12" s="13"/>
+      <x:c r="B12" s="13" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="B13" s="9"/>
-      <x:c r="C13" s="9"/>
-      <x:c r="D13" s="9"/>
-      <x:c r="E13" s="9"/>
-      <x:c r="F13" s="9"/>
-      <x:c r="G13" s="10" t="s">
+      <x:c r="C12" s="13"/>
+      <x:c r="D12" s="13" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="H13" s="3"/>
-      <x:c r="I13" s="3"/>
-      <x:c r="J13" s="3"/>
-      <x:c r="K13" s="3"/>
-    </x:row>
-    <x:row r="14" spans="1:11">
-      <x:c r="A14" s="4"/>
-      <x:c r="B14" s="4"/>
-      <x:c r="C14" s="4"/>
-      <x:c r="D14" s="4"/>
-      <x:c r="E14" s="4"/>
-      <x:c r="F14" s="4"/>
-      <x:c r="G14" s="4"/>
+      <x:c r="E12" s="13" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F12" s="13" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G12" s="13" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H12" s="13" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="I12" s="13" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="J12" s="13" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="K12" s="3"/>
+    </x:row>
+    <x:row r="13" spans="1:11">
+      <x:c r="A13" s="4"/>
+      <x:c r="B13" s="4"/>
+      <x:c r="C13" s="4"/>
+      <x:c r="D13" s="4"/>
+      <x:c r="E13" s="4"/>
+      <x:c r="F13" s="4"/>
+      <x:c r="G13" s="4"/>
+      <x:c r="H13" s="4"/>
+      <x:c r="I13" s="4"/>
+      <x:c r="J13" s="4"/>
+      <x:c r="K13" s="4"/>
+    </x:row>
+    <x:row r="14" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A14" s="8" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B14" s="9"/>
+      <x:c r="C14" s="9"/>
+      <x:c r="D14" s="9"/>
+      <x:c r="E14" s="9"/>
+      <x:c r="F14" s="9"/>
+      <x:c r="G14" s="10" t="s">
+        <x:v>39</x:v>
+      </x:c>
       <x:c r="H14" s="3"/>
       <x:c r="I14" s="3"/>
       <x:c r="J14" s="3"/>
       <x:c r="K14" s="3"/>
     </x:row>
-    <x:row r="15" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A15" s="11" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="B15" s="11" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C15" s="11" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="D15" s="11" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E15" s="11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="F15" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G15" s="11" t="s">
-        <x:v>17</x:v>
-      </x:c>
+    <x:row r="15" spans="1:11">
+      <x:c r="A15" s="4"/>
+      <x:c r="B15" s="4"/>
+      <x:c r="C15" s="4"/>
+      <x:c r="D15" s="4"/>
+      <x:c r="E15" s="4"/>
+      <x:c r="F15" s="4"/>
+      <x:c r="G15" s="4"/>
       <x:c r="H15" s="3"/>
       <x:c r="I15" s="3"/>
       <x:c r="J15" s="3"/>
       <x:c r="K15" s="3"/>
     </x:row>
-    <x:row r="16" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A16" s="12" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="B16" s="12" t="s">
+    <x:row r="16" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A16" s="11" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C16" s="12" t="s">
+      <x:c r="B16" s="11" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="D16" s="12" t="s">
+      <x:c r="C16" s="11" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="E16" s="12" t="s">
+      <x:c r="D16" s="11" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="F16" s="12" t="s">
+      <x:c r="E16" s="11" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="G16" s="12" t="s">
-        <x:v>45</x:v>
+      <x:c r="F16" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G16" s="11" t="s">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="H16" s="3"/>
       <x:c r="I16" s="3"/>
@@ -1090,10 +1113,10 @@
     </x:row>
     <x:row r="17" spans="1:11" ht="30" customHeight="1">
       <x:c r="A17" s="12" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B17" s="12" t="s">
         <x:v>46</x:v>
-      </x:c>
-      <x:c r="B17" s="12" t="s">
-        <x:v>40</x:v>
       </x:c>
       <x:c r="C17" s="12" t="s">
         <x:v>47</x:v>
@@ -1102,13 +1125,13 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="E17" s="12" t="s">
-        <x:v>43</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F17" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G17" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H17" s="3"/>
       <x:c r="I17" s="3"/>
@@ -1116,143 +1139,170 @@
       <x:c r="K17" s="3"/>
     </x:row>
     <x:row r="18" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A18" s="13" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="B18" s="13" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C18" s="13" t="s">
+      <x:c r="A18" s="12" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="D18" s="13" t="s">
+      <x:c r="B18" s="12" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="E18" s="13" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="F18" s="13" t="s">
+      <x:c r="C18" s="12" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="G18" s="13" t="s">
+      <x:c r="D18" s="12" t="s">
         <x:v>55</x:v>
+      </x:c>
+      <x:c r="E18" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="F18" s="12" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="G18" s="12" t="s">
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H18" s="3"/>
       <x:c r="I18" s="3"/>
       <x:c r="J18" s="3"/>
       <x:c r="K18" s="3"/>
     </x:row>
-    <x:row r="19" spans="1:11">
-      <x:c r="A19" s="4"/>
-      <x:c r="B19" s="4"/>
-      <x:c r="C19" s="4"/>
-      <x:c r="D19" s="4"/>
-      <x:c r="E19" s="4"/>
-      <x:c r="F19" s="4"/>
-      <x:c r="G19" s="4"/>
-      <x:c r="H19" s="4"/>
-      <x:c r="I19" s="4"/>
-      <x:c r="J19" s="4"/>
-      <x:c r="K19" s="4"/>
-    </x:row>
-    <x:row r="20" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A20" s="8" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="B20" s="9"/>
-      <x:c r="C20" s="9"/>
-      <x:c r="D20" s="9"/>
-      <x:c r="E20" s="9"/>
-      <x:c r="F20" s="9"/>
-      <x:c r="G20" s="9"/>
-      <x:c r="H20" s="9"/>
-      <x:c r="I20" s="9"/>
-      <x:c r="J20" s="9"/>
-      <x:c r="K20" s="10" t="s">
-        <x:v>57</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:11">
-      <x:c r="A21" s="4"/>
-      <x:c r="B21" s="4"/>
-      <x:c r="C21" s="4"/>
-      <x:c r="D21" s="4"/>
-      <x:c r="E21" s="4"/>
-      <x:c r="F21" s="4"/>
-      <x:c r="G21" s="4"/>
-      <x:c r="H21" s="4"/>
-      <x:c r="I21" s="4"/>
-      <x:c r="J21" s="4"/>
-      <x:c r="K21" s="4"/>
-    </x:row>
-    <x:row r="22" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A22" s="11" t="s">
+    <x:row r="19" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A19" s="13" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B19" s="13" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C19" s="13" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="D19" s="13" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E19" s="13" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="F19" s="13" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="G19" s="13" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="H19" s="3"/>
+      <x:c r="I19" s="3"/>
+      <x:c r="J19" s="3"/>
+      <x:c r="K19" s="3"/>
+    </x:row>
+    <x:row r="20" spans="1:11">
+      <x:c r="A20" s="4"/>
+      <x:c r="B20" s="4"/>
+      <x:c r="C20" s="4"/>
+      <x:c r="D20" s="4"/>
+      <x:c r="E20" s="4"/>
+      <x:c r="F20" s="4"/>
+      <x:c r="G20" s="4"/>
+      <x:c r="H20" s="4"/>
+      <x:c r="I20" s="4"/>
+      <x:c r="J20" s="4"/>
+      <x:c r="K20" s="4"/>
+    </x:row>
+    <x:row r="21" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A21" s="8" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B21" s="9"/>
+      <x:c r="C21" s="9"/>
+      <x:c r="D21" s="9"/>
+      <x:c r="E21" s="9"/>
+      <x:c r="F21" s="9"/>
+      <x:c r="G21" s="9"/>
+      <x:c r="H21" s="9"/>
+      <x:c r="I21" s="9"/>
+      <x:c r="J21" s="9"/>
+      <x:c r="K21" s="10" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:11">
+      <x:c r="A22" s="4"/>
+      <x:c r="B22" s="4"/>
+      <x:c r="C22" s="4"/>
+      <x:c r="D22" s="4"/>
+      <x:c r="E22" s="4"/>
+      <x:c r="F22" s="4"/>
+      <x:c r="G22" s="4"/>
+      <x:c r="H22" s="4"/>
+      <x:c r="I22" s="4"/>
+      <x:c r="J22" s="4"/>
+      <x:c r="K22" s="4"/>
+    </x:row>
+    <x:row r="23" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A23" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B22" s="11" t="s">
+      <x:c r="B23" s="11" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C22" s="11" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="D22" s="11" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="E22" s="11" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="F22" s="11" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="G22" s="11" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="H22" s="11" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="I22" s="11" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="J22" s="11" t="s">
+      <x:c r="C23" s="11" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="K22" s="11" t="s">
+      <x:c r="D23" s="11" t="s">
         <x:v>66</x:v>
       </x:c>
-    </x:row>
-    <x:row r="23" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A23" s="13" t="s">
+      <x:c r="E23" s="11" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="B23" s="13" t="s">
+      <x:c r="F23" s="11" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="C23" s="13" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="D23" s="13" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="E23" s="13" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="F23" s="13" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="G23" s="13" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="H23" s="13" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="I23" s="13" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="J23" s="13" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="K23" s="13" t="s">
-        <x:v>68</x:v>
+      <x:c r="G23" s="11" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="H23" s="11" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="I23" s="11" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="J23" s="11" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="K23" s="11" t="s">
+        <x:v>73</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A24" s="13" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B24" s="13" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C24" s="13" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D24" s="13" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="E24" s="13" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="F24" s="13" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="G24" s="13" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="H24" s="13" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="I24" s="13" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="J24" s="13" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="K24" s="13" t="s">
+        <x:v>75</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1260,8 +1310,8 @@
     <x:mergeCell ref="A1:E1"/>
     <x:mergeCell ref="F1:G1"/>
     <x:mergeCell ref="A7:F7"/>
-    <x:mergeCell ref="A13:F13"/>
-    <x:mergeCell ref="A20:J20"/>
+    <x:mergeCell ref="A14:F14"/>
+    <x:mergeCell ref="A21:J21"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/data/positions/Posição Consolidada - 5166121.xlsx
+++ b/data/positions/Posição Consolidada - 5166121.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 5166121 | 16/09/2026, 08:42</x:t>
+    <x:t>Conta: 5166121 | 21/09/2026, 16:40</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,13 +34,13 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>42,4%|Operações Compromissadas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 3.713.608,72</x:t>
-  </x:si>
-  <x:si>
-    <x:t>42,30%|Pós-Fixada</x:t>
+    <x:t>41,0%|Operações Compromissadas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 4.914.768,12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>41,00%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -70,46 +70,28 @@
     <x:t>Valor líquido</x:t>
   </x:si>
   <x:si>
-    <x:t>28/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29/09/2026</x:t>
+    <x:t>31/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01/10/2026</x:t>
   </x:si>
   <x:si>
     <x:t>85,00% CDI</x:t>
   </x:si>
   <x:si>
-    <x:t>850,00</x:t>
+    <x:t>326,00</x:t>
   </x:si>
   <x:si>
     <x:t>0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.204.819,28</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.211.183,21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.209.751,33</x:t>
-  </x:si>
-  <x:si>
-    <x:t>31/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01/10/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2.950,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 996.285,04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.001.107,88</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.000.022,74</x:t>
+    <x:t>R$ 110.097,94</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 110.775,07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 110.622,72</x:t>
   </x:si>
   <x:si>
     <x:t>14/09/2026</x:t>
@@ -118,25 +100,52 @@
     <x:t>14/10/2026</x:t>
   </x:si>
   <x:si>
-    <x:t>882.352,00</x:t>
+    <x:t>882.318,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.499.942,20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.503.216,01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.502.479,40</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22/10/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.028.571,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.799.999,99</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.800.777,05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.800.602,21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>937.500,00</x:t>
   </x:si>
   <x:si>
     <x:t>R$ 1.500.000,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.501.317,62</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.501.021,15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>57,6%|Fundos de Investimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.048.539,86</x:t>
-  </x:si>
-  <x:si>
-    <x:t>57,50%|Fundos de Renda Fixa Pós-Fixado</x:t>
+    <x:t>59,0%|Fundos de Investimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 7.063.207,55</x:t>
+  </x:si>
+  <x:si>
+    <x:t>58,90%|Fundos de Renda Fixa Pós-Fixado</x:t>
   </x:si>
   <x:si>
     <x:t>Data cota</x:t>
@@ -154,10 +163,7 @@
     <x:t>Safra DI Master FIRF Referenciado DI LP</x:t>
   </x:si>
   <x:si>
-    <x:t>15/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 274,26</x:t>
+    <x:t>R$ 274,82</x:t>
   </x:si>
   <x:si>
     <x:t>7.363,69</x:t>
@@ -166,49 +172,58 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.019.561,80</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.014.250,78</x:t>
+    <x:t>R$ 2.023.678,59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.018.350,91</x:t>
+  </x:si>
+  <x:si>
+    <x:t>XP Bancos FIRF Referenciada DI CP RL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1,95</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.030.619,91</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.005.221,23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.003.322,14</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
   </x:si>
   <x:si>
-    <x:t>16/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.452,18</x:t>
+    <x:t>R$ 1.454,48</x:t>
   </x:si>
   <x:si>
     <x:t>1.390,64</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.019.467,79</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.014.182,29</x:t>
+    <x:t>R$ 2.022.662,72</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.017.563,61</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1,48</x:t>
+    <x:t>R$ 1,49</x:t>
   </x:si>
   <x:si>
     <x:t>680.719,86</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.009.510,27</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.006.633,42</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0,04%|Saldo projetado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 3.089,05</x:t>
+    <x:t>R$ 1.011.645,01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.009.024,89</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 0,18</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -238,7 +253,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>3089,05</x:t>
+    <x:t>0,18</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -786,7 +801,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K24"/>
+  <x:dimension ref="A1:K26"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="38.282054" style="0" customWidth="1"/>
@@ -846,13 +861,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>8765237.62675774</x:v>
+        <x:v>11977975.8517347</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>8762148.57675774</x:v>
+        <x:v>11977975.6717347</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>3089.05</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
@@ -1013,125 +1028,127 @@
       <x:c r="K11" s="3"/>
     </x:row>
     <x:row r="12" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A12" s="13"/>
-      <x:c r="B12" s="13" t="s">
+      <x:c r="A12" s="12"/>
+      <x:c r="B12" s="12" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C12" s="13"/>
-      <x:c r="D12" s="13" t="s">
+      <x:c r="C12" s="12"/>
+      <x:c r="D12" s="12" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="E12" s="13" t="s">
+      <x:c r="E12" s="12" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="F12" s="13" t="s">
+      <x:c r="F12" s="12" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="G12" s="13" t="s">
+      <x:c r="G12" s="12" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="H12" s="13" t="s">
+      <x:c r="H12" s="12" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="I12" s="13" t="s">
+      <x:c r="I12" s="12" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="J12" s="13" t="s">
+      <x:c r="J12" s="12" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="K12" s="3"/>
     </x:row>
-    <x:row r="13" spans="1:11">
-      <x:c r="A13" s="4"/>
-      <x:c r="B13" s="4"/>
-      <x:c r="C13" s="4"/>
-      <x:c r="D13" s="4"/>
-      <x:c r="E13" s="4"/>
-      <x:c r="F13" s="4"/>
-      <x:c r="G13" s="4"/>
-      <x:c r="H13" s="4"/>
-      <x:c r="I13" s="4"/>
-      <x:c r="J13" s="4"/>
-      <x:c r="K13" s="4"/>
-    </x:row>
-    <x:row r="14" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A14" s="8" t="s">
+    <x:row r="13" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A13" s="13"/>
+      <x:c r="B13" s="13" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="B14" s="9"/>
-      <x:c r="C14" s="9"/>
-      <x:c r="D14" s="9"/>
-      <x:c r="E14" s="9"/>
-      <x:c r="F14" s="9"/>
-      <x:c r="G14" s="10" t="s">
+      <x:c r="C13" s="13"/>
+      <x:c r="D13" s="13" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E13" s="13" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F13" s="13" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="H14" s="3"/>
-      <x:c r="I14" s="3"/>
-      <x:c r="J14" s="3"/>
-      <x:c r="K14" s="3"/>
-    </x:row>
-    <x:row r="15" spans="1:11">
-      <x:c r="A15" s="4"/>
-      <x:c r="B15" s="4"/>
-      <x:c r="C15" s="4"/>
-      <x:c r="D15" s="4"/>
-      <x:c r="E15" s="4"/>
-      <x:c r="F15" s="4"/>
-      <x:c r="G15" s="4"/>
+      <x:c r="G13" s="13" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H13" s="13" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="I13" s="13" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="J13" s="13" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="K13" s="3"/>
+    </x:row>
+    <x:row r="14" spans="1:11">
+      <x:c r="A14" s="4"/>
+      <x:c r="B14" s="4"/>
+      <x:c r="C14" s="4"/>
+      <x:c r="D14" s="4"/>
+      <x:c r="E14" s="4"/>
+      <x:c r="F14" s="4"/>
+      <x:c r="G14" s="4"/>
+      <x:c r="H14" s="4"/>
+      <x:c r="I14" s="4"/>
+      <x:c r="J14" s="4"/>
+      <x:c r="K14" s="4"/>
+    </x:row>
+    <x:row r="15" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A15" s="8" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B15" s="9"/>
+      <x:c r="C15" s="9"/>
+      <x:c r="D15" s="9"/>
+      <x:c r="E15" s="9"/>
+      <x:c r="F15" s="9"/>
+      <x:c r="G15" s="10" t="s">
+        <x:v>42</x:v>
+      </x:c>
       <x:c r="H15" s="3"/>
       <x:c r="I15" s="3"/>
       <x:c r="J15" s="3"/>
       <x:c r="K15" s="3"/>
     </x:row>
-    <x:row r="16" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A16" s="11" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="B16" s="11" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C16" s="11" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="D16" s="11" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E16" s="11" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="F16" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G16" s="11" t="s">
-        <x:v>17</x:v>
-      </x:c>
+    <x:row r="16" spans="1:11">
+      <x:c r="A16" s="4"/>
+      <x:c r="B16" s="4"/>
+      <x:c r="C16" s="4"/>
+      <x:c r="D16" s="4"/>
+      <x:c r="E16" s="4"/>
+      <x:c r="F16" s="4"/>
+      <x:c r="G16" s="4"/>
       <x:c r="H16" s="3"/>
       <x:c r="I16" s="3"/>
       <x:c r="J16" s="3"/>
       <x:c r="K16" s="3"/>
     </x:row>
-    <x:row r="17" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A17" s="12" t="s">
+    <x:row r="17" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A17" s="11" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B17" s="11" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C17" s="11" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="B17" s="12" t="s">
+      <x:c r="D17" s="11" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="C17" s="12" t="s">
+      <x:c r="E17" s="11" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="D17" s="12" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="E17" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="F17" s="12" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="G17" s="12" t="s">
-        <x:v>51</x:v>
+      <x:c r="F17" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G17" s="11" t="s">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="H17" s="3"/>
       <x:c r="I17" s="3"/>
@@ -1140,25 +1157,25 @@
     </x:row>
     <x:row r="18" spans="1:11" ht="30" customHeight="1">
       <x:c r="A18" s="12" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B18" s="12" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C18" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D18" s="12" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E18" s="12" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="F18" s="12" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="B18" s="12" t="s">
+      <x:c r="G18" s="12" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="C18" s="12" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="D18" s="12" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E18" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="F18" s="12" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="G18" s="12" t="s">
-        <x:v>57</x:v>
       </x:c>
       <x:c r="H18" s="3"/>
       <x:c r="I18" s="3"/>
@@ -1166,61 +1183,85 @@
       <x:c r="K18" s="3"/>
     </x:row>
     <x:row r="19" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A19" s="13" t="s">
+      <x:c r="A19" s="12" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B19" s="12" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C19" s="12" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="D19" s="12" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="E19" s="12" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="F19" s="12" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="G19" s="12" t="s">
         <x:v>58</x:v>
-      </x:c>
-      <x:c r="B19" s="13" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C19" s="13" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="D19" s="13" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="E19" s="13" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="F19" s="13" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="G19" s="13" t="s">
-        <x:v>62</x:v>
       </x:c>
       <x:c r="H19" s="3"/>
       <x:c r="I19" s="3"/>
       <x:c r="J19" s="3"/>
       <x:c r="K19" s="3"/>
     </x:row>
-    <x:row r="20" spans="1:11">
-      <x:c r="A20" s="4"/>
-      <x:c r="B20" s="4"/>
-      <x:c r="C20" s="4"/>
-      <x:c r="D20" s="4"/>
-      <x:c r="E20" s="4"/>
-      <x:c r="F20" s="4"/>
-      <x:c r="G20" s="4"/>
-      <x:c r="H20" s="4"/>
-      <x:c r="I20" s="4"/>
-      <x:c r="J20" s="4"/>
-      <x:c r="K20" s="4"/>
-    </x:row>
-    <x:row r="21" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A21" s="8" t="s">
+    <x:row r="20" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A20" s="12" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B20" s="12" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C20" s="12" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D20" s="12" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E20" s="12" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="F20" s="12" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="G20" s="12" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="B21" s="9"/>
-      <x:c r="C21" s="9"/>
-      <x:c r="D21" s="9"/>
-      <x:c r="E21" s="9"/>
-      <x:c r="F21" s="9"/>
-      <x:c r="G21" s="9"/>
-      <x:c r="H21" s="9"/>
-      <x:c r="I21" s="9"/>
-      <x:c r="J21" s="9"/>
-      <x:c r="K21" s="10" t="s">
+      <x:c r="H20" s="3"/>
+      <x:c r="I20" s="3"/>
+      <x:c r="J20" s="3"/>
+      <x:c r="K20" s="3"/>
+    </x:row>
+    <x:row r="21" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A21" s="13" t="s">
         <x:v>64</x:v>
       </x:c>
+      <x:c r="B21" s="13" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C21" s="13" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="D21" s="13" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E21" s="13" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="F21" s="13" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="G21" s="13" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="H21" s="3"/>
+      <x:c r="I21" s="3"/>
+      <x:c r="J21" s="3"/>
+      <x:c r="K21" s="3"/>
     </x:row>
     <x:row r="22" spans="1:11">
       <x:c r="A22" s="4"/>
@@ -1235,74 +1276,104 @@
       <x:c r="J22" s="4"/>
       <x:c r="K22" s="4"/>
     </x:row>
-    <x:row r="23" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A23" s="11" t="s">
+    <x:row r="23" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A23" s="8" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B23" s="9"/>
+      <x:c r="C23" s="9"/>
+      <x:c r="D23" s="9"/>
+      <x:c r="E23" s="9"/>
+      <x:c r="F23" s="9"/>
+      <x:c r="G23" s="9"/>
+      <x:c r="H23" s="9"/>
+      <x:c r="I23" s="9"/>
+      <x:c r="J23" s="9"/>
+      <x:c r="K23" s="10" t="s">
+        <x:v>69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:11">
+      <x:c r="A24" s="4"/>
+      <x:c r="B24" s="4"/>
+      <x:c r="C24" s="4"/>
+      <x:c r="D24" s="4"/>
+      <x:c r="E24" s="4"/>
+      <x:c r="F24" s="4"/>
+      <x:c r="G24" s="4"/>
+      <x:c r="H24" s="4"/>
+      <x:c r="I24" s="4"/>
+      <x:c r="J24" s="4"/>
+      <x:c r="K24" s="4"/>
+    </x:row>
+    <x:row r="25" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A25" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B23" s="11" t="s">
+      <x:c r="B25" s="11" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C23" s="11" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="D23" s="11" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E23" s="11" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="F23" s="11" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="G23" s="11" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="H23" s="11" t="s">
+      <x:c r="C25" s="11" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="I23" s="11" t="s">
+      <x:c r="D25" s="11" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="J23" s="11" t="s">
+      <x:c r="E25" s="11" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="K23" s="11" t="s">
+      <x:c r="F25" s="11" t="s">
         <x:v>73</x:v>
       </x:c>
-    </x:row>
-    <x:row r="24" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A24" s="13" t="s">
+      <x:c r="G25" s="11" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="B24" s="13" t="s">
+      <x:c r="H25" s="11" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="C24" s="13" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="D24" s="13" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="E24" s="13" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="F24" s="13" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="G24" s="13" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="H24" s="13" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="I24" s="13" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="J24" s="13" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="K24" s="13" t="s">
-        <x:v>75</x:v>
+      <x:c r="I25" s="11" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="J25" s="11" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="K25" s="11" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A26" s="13" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B26" s="13" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C26" s="13" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D26" s="13" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E26" s="13" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="F26" s="13" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="G26" s="13" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="H26" s="13" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="I26" s="13" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="J26" s="13" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="K26" s="13" t="s">
+        <x:v>80</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1310,8 +1381,8 @@
     <x:mergeCell ref="A1:E1"/>
     <x:mergeCell ref="F1:G1"/>
     <x:mergeCell ref="A7:F7"/>
-    <x:mergeCell ref="A14:F14"/>
-    <x:mergeCell ref="A21:J21"/>
+    <x:mergeCell ref="A15:F15"/>
+    <x:mergeCell ref="A23:J23"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/data/positions/Posição Consolidada - 5166121.xlsx
+++ b/data/positions/Posição Consolidada - 5166121.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 5166121 | 21/09/2026, 16:40</x:t>
+    <x:t>Conta: 5166121 | 23/09/2026, 09:36</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>41,0%|Operações Compromissadas</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 4.914.768,12</x:t>
+    <x:t>R$ 4.919.012,43</x:t>
   </x:si>
   <x:si>
     <x:t>41,00%|Pós-Fixada</x:t>
@@ -88,10 +88,10 @@
     <x:t>R$ 110.097,94</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 110.775,07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 110.622,72</x:t>
+    <x:t>R$ 110.870,73</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 110.696,85</x:t>
   </x:si>
   <x:si>
     <x:t>14/09/2026</x:t>
@@ -106,10 +106,10 @@
     <x:t>R$ 1.499.942,20</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.503.216,01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.502.479,40</x:t>
+    <x:t>R$ 1.504.514,17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.503.485,48</x:t>
   </x:si>
   <x:si>
     <x:t>18/09/2026</x:t>
@@ -124,10 +124,10 @@
     <x:t>R$ 1.799.999,99</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.800.777,05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.800.602,21</x:t>
+    <x:t>R$ 1.802.332,16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.801.807,42</x:t>
   </x:si>
   <x:si>
     <x:t>21/09/2026</x:t>
@@ -139,10 +139,16 @@
     <x:t>R$ 1.500.000,00</x:t>
   </x:si>
   <x:si>
+    <x:t>R$ 1.501.295,37</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.501.003,91</x:t>
+  </x:si>
+  <x:si>
     <x:t>59,0%|Fundos de Investimento</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 7.063.207,55</x:t>
+    <x:t>R$ 7.069.178,32</x:t>
   </x:si>
   <x:si>
     <x:t>58,90%|Fundos de Renda Fixa Pós-Fixado</x:t>
@@ -163,7 +169,10 @@
     <x:t>Safra DI Master FIRF Referenciado DI LP</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 274,82</x:t>
+    <x:t>22/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 274,96</x:t>
   </x:si>
   <x:si>
     <x:t>7.363,69</x:t>
@@ -172,40 +181,43 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.023.678,59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.018.350,91</x:t>
+    <x:t>R$ 2.024.690,89</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.019.135,44</x:t>
   </x:si>
   <x:si>
     <x:t>XP Bancos FIRF Referenciada DI CP RL</x:t>
   </x:si>
   <x:si>
+    <x:t>23/09/2026</x:t>
+  </x:si>
+  <x:si>
     <x:t>R$ 1,95</x:t>
   </x:si>
   <x:si>
     <x:t>1.030.619,91</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.005.221,23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.003.322,14</x:t>
+    <x:t>R$ 2.007.188,28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.003.726,09</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.454,48</x:t>
+    <x:t>R$ 1.455,89</x:t>
   </x:si>
   <x:si>
     <x:t>1.390,64</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.022.662,72</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.017.563,61</x:t>
+    <x:t>R$ 2.024.616,18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.019.077,54</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
@@ -217,10 +229,10 @@
     <x:t>680.719,86</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.011.645,01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.009.024,89</x:t>
+    <x:t>R$ 1.012.682,97</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.009.829,30</x:t>
   </x:si>
   <x:si>
     <x:t>R$ 0,18</x:t>
@@ -861,10 +873,10 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>11977975.8517347</x:v>
+        <x:v>11988190.9285421</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>11977975.6717347</x:v>
+        <x:v>11988190.7485421</x:v>
       </x:c>
       <x:c r="C4" s="7">
         <x:v>0.18</x:v>
@@ -1078,10 +1090,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="I13" s="13" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="J13" s="13" t="s">
-        <x:v>40</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="K13" s="3"/>
     </x:row>
@@ -1100,7 +1112,7 @@
     </x:row>
     <x:row r="15" spans="1:11" ht="45" customHeight="1">
       <x:c r="A15" s="8" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B15" s="9"/>
       <x:c r="C15" s="9"/>
@@ -1108,7 +1120,7 @@
       <x:c r="E15" s="9"/>
       <x:c r="F15" s="9"/>
       <x:c r="G15" s="10" t="s">
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H15" s="3"/>
       <x:c r="I15" s="3"/>
@@ -1130,19 +1142,19 @@
     </x:row>
     <x:row r="17" spans="1:11" ht="35.1" customHeight="1">
       <x:c r="A17" s="11" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B17" s="11" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C17" s="11" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D17" s="11" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E17" s="11" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F17" s="11" t="s">
         <x:v>16</x:v>
@@ -1157,25 +1169,25 @@
     </x:row>
     <x:row r="18" spans="1:11" ht="30" customHeight="1">
       <x:c r="A18" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B18" s="12" t="s">
-        <x:v>38</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C18" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D18" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E18" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F18" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G18" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H18" s="3"/>
       <x:c r="I18" s="3"/>
@@ -1184,25 +1196,25 @@
     </x:row>
     <x:row r="19" spans="1:11" ht="30" customHeight="1">
       <x:c r="A19" s="12" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B19" s="12" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C19" s="12" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="D19" s="12" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E19" s="12" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="B19" s="12" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C19" s="12" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="D19" s="12" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E19" s="12" t="s">
-        <x:v>51</x:v>
-      </x:c>
       <x:c r="F19" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G19" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="H19" s="3"/>
       <x:c r="I19" s="3"/>
@@ -1211,25 +1223,25 @@
     </x:row>
     <x:row r="20" spans="1:11" ht="30" customHeight="1">
       <x:c r="A20" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B20" s="12" t="s">
-        <x:v>38</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C20" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D20" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E20" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F20" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="G20" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H20" s="3"/>
       <x:c r="I20" s="3"/>
@@ -1238,25 +1250,25 @@
     </x:row>
     <x:row r="21" spans="1:11" ht="30" customHeight="1">
       <x:c r="A21" s="13" t="s">
-        <x:v>64</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B21" s="13" t="s">
-        <x:v>38</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C21" s="13" t="s">
-        <x:v>65</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D21" s="13" t="s">
-        <x:v>66</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E21" s="13" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F21" s="13" t="s">
-        <x:v>67</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="G21" s="13" t="s">
-        <x:v>68</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="H21" s="3"/>
       <x:c r="I21" s="3"/>
@@ -1290,7 +1302,7 @@
       <x:c r="I23" s="9"/>
       <x:c r="J23" s="9"/>
       <x:c r="K23" s="10" t="s">
-        <x:v>69</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:11">
@@ -1314,66 +1326,66 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C25" s="11" t="s">
-        <x:v>70</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D25" s="11" t="s">
-        <x:v>71</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E25" s="11" t="s">
-        <x:v>72</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="F25" s="11" t="s">
-        <x:v>73</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="G25" s="11" t="s">
-        <x:v>74</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="H25" s="11" t="s">
-        <x:v>75</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="I25" s="11" t="s">
-        <x:v>76</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="J25" s="11" t="s">
-        <x:v>77</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="K25" s="11" t="s">
-        <x:v>78</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:11" ht="30" customHeight="1">
       <x:c r="A26" s="13" t="s">
-        <x:v>79</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B26" s="13" t="s">
-        <x:v>80</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C26" s="13" t="s">
-        <x:v>80</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D26" s="13" t="s">
-        <x:v>80</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E26" s="13" t="s">
-        <x:v>80</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="F26" s="13" t="s">
-        <x:v>80</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="G26" s="13" t="s">
-        <x:v>80</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="H26" s="13" t="s">
-        <x:v>80</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="I26" s="13" t="s">
-        <x:v>80</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="J26" s="13" t="s">
-        <x:v>80</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="K26" s="13" t="s">
-        <x:v>80</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/data/positions/Posição Consolidada - 5166121.xlsx
+++ b/data/positions/Posição Consolidada - 5166121.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 5166121 | 23/09/2026, 09:36</x:t>
+    <x:t>Conta: 5166121 | 30/09/2026, 08:52</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,13 +34,13 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>41,0%|Operações Compromissadas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 4.919.012,43</x:t>
-  </x:si>
-  <x:si>
-    <x:t>41,00%|Pós-Fixada</x:t>
+    <x:t>62,2%|Operações Compromissadas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 11.639.240,31</x:t>
+  </x:si>
+  <x:si>
+    <x:t>62,10%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -70,46 +70,28 @@
     <x:t>Valor líquido</x:t>
   </x:si>
   <x:si>
-    <x:t>31/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01/10/2026</x:t>
+    <x:t>14/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14/10/2026</x:t>
   </x:si>
   <x:si>
     <x:t>85,00% CDI</x:t>
   </x:si>
   <x:si>
-    <x:t>326,00</x:t>
+    <x:t>771.462,00</x:t>
   </x:si>
   <x:si>
     <x:t>0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 110.097,94</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 110.870,73</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 110.696,85</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14/10/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>882.318,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.499.942,20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.504.514,17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.503.485,48</x:t>
+    <x:t>R$ 1.311.486,80</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.318.326,25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.316.787,37</x:t>
   </x:si>
   <x:si>
     <x:t>18/09/2026</x:t>
@@ -124,10 +106,10 @@
     <x:t>R$ 1.799.999,99</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.802.332,16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.801.807,42</x:t>
+    <x:t>R$ 1.806.225,84</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.804.825,02</x:t>
   </x:si>
   <x:si>
     <x:t>21/09/2026</x:t>
@@ -139,19 +121,73 @@
     <x:t>R$ 1.500.000,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.501.295,37</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.501.003,91</x:t>
-  </x:si>
-  <x:si>
-    <x:t>59,0%|Fundos de Investimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 7.069.178,32</x:t>
-  </x:si>
-  <x:si>
-    <x:t>58,90%|Fundos de Renda Fixa Pós-Fixado</x:t>
+    <x:t>R$ 1.504.538,70</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.503.517,49</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27/10/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.562.499,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.499.998,40</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.505.399,27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.504.184,07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29/10/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.156.069,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.999.999,99</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.002.591,30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.002.008,26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30/10/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.420.454,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.499.999,99</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.502.158,95</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.501.673,18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>37,8%|Fundos de Investimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 7.085.739,96</x:t>
+  </x:si>
+  <x:si>
+    <x:t>37,80%|Fundos de Renda Fixa Pós-Fixado</x:t>
   </x:si>
   <x:si>
     <x:t>Data cota</x:t>
@@ -169,10 +205,10 @@
     <x:t>Safra DI Master FIRF Referenciado DI LP</x:t>
   </x:si>
   <x:si>
-    <x:t>22/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 274,96</x:t>
+    <x:t>29/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 275,61</x:t>
   </x:si>
   <x:si>
     <x:t>7.363,69</x:t>
@@ -181,43 +217,43 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.024.690,89</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.019.135,44</x:t>
+    <x:t>R$ 2.029.530,77</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.022.886,35</x:t>
   </x:si>
   <x:si>
     <x:t>XP Bancos FIRF Referenciada DI CP RL</x:t>
   </x:si>
   <x:si>
-    <x:t>23/09/2026</x:t>
-  </x:si>
-  <x:si>
     <x:t>R$ 1,95</x:t>
   </x:si>
   <x:si>
     <x:t>1.030.619,91</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.007.188,28</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.003.726,09</x:t>
+    <x:t>R$ 2.011.391,93</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.005.664,30</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.455,89</x:t>
+    <x:t>30/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.459,43</x:t>
   </x:si>
   <x:si>
     <x:t>1.390,64</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.024.616,18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.019.077,54</x:t>
+    <x:t>R$ 2.029.548,24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.022.899,89</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
@@ -229,13 +265,13 @@
     <x:t>680.719,86</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.012.682,97</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.009.829,30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 0,18</x:t>
+    <x:t>R$ 1.015.269,02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.011.833,49</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 0,85</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -265,7 +301,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>0,18</x:t>
+    <x:t>0,85</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -813,7 +849,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K26"/>
+  <x:dimension ref="A1:K28"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="38.282054" style="0" customWidth="1"/>
@@ -873,13 +909,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>11988190.9285421</x:v>
+        <x:v>18724981.1202784</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>11988190.7485421</x:v>
+        <x:v>18724980.2702784</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>0.18</x:v>
+        <x:v>0.85</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
@@ -1046,85 +1082,113 @@
       </x:c>
       <x:c r="C12" s="12"/>
       <x:c r="D12" s="12" t="s">
-        <x:v>33</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E12" s="12" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="F12" s="12" t="s">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G12" s="12" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="H12" s="12" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="I12" s="12" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="I12" s="12" t="s">
+      <x:c r="J12" s="12" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="J12" s="12" t="s">
+      <x:c r="K12" s="3"/>
+    </x:row>
+    <x:row r="13" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A13" s="12"/>
+      <x:c r="B13" s="12" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="K12" s="3"/>
-    </x:row>
-    <x:row r="13" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A13" s="13"/>
-      <x:c r="B13" s="13" t="s">
+      <x:c r="C13" s="12"/>
+      <x:c r="D13" s="12" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C13" s="13"/>
-      <x:c r="D13" s="13" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E13" s="13" t="s">
+      <x:c r="E13" s="12" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="F13" s="13" t="s">
+      <x:c r="F13" s="12" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="G13" s="13" t="s">
+      <x:c r="G13" s="12" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="H13" s="13" t="s">
+      <x:c r="H13" s="12" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="I13" s="13" t="s">
+      <x:c r="I13" s="12" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="J13" s="13" t="s">
+      <x:c r="J13" s="12" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="K13" s="3"/>
     </x:row>
-    <x:row r="14" spans="1:11">
-      <x:c r="A14" s="4"/>
-      <x:c r="B14" s="4"/>
-      <x:c r="C14" s="4"/>
-      <x:c r="D14" s="4"/>
-      <x:c r="E14" s="4"/>
-      <x:c r="F14" s="4"/>
-      <x:c r="G14" s="4"/>
-      <x:c r="H14" s="4"/>
-      <x:c r="I14" s="4"/>
-      <x:c r="J14" s="4"/>
-      <x:c r="K14" s="4"/>
-    </x:row>
-    <x:row r="15" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A15" s="8" t="s">
+    <x:row r="14" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A14" s="12"/>
+      <x:c r="B14" s="12" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="B15" s="9"/>
-      <x:c r="C15" s="9"/>
-      <x:c r="D15" s="9"/>
-      <x:c r="E15" s="9"/>
-      <x:c r="F15" s="9"/>
-      <x:c r="G15" s="10" t="s">
+      <x:c r="C14" s="12"/>
+      <x:c r="D14" s="12" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="H15" s="3"/>
-      <x:c r="I15" s="3"/>
-      <x:c r="J15" s="3"/>
+      <x:c r="E14" s="12" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F14" s="12" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G14" s="12" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H14" s="12" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="I14" s="12" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="J14" s="12" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="K14" s="3"/>
+    </x:row>
+    <x:row r="15" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A15" s="13"/>
+      <x:c r="B15" s="13" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C15" s="13"/>
+      <x:c r="D15" s="13" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E15" s="13" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F15" s="13" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="G15" s="13" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H15" s="13" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="I15" s="13" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="J15" s="13" t="s">
+        <x:v>54</x:v>
+      </x:c>
       <x:c r="K15" s="3"/>
     </x:row>
     <x:row r="16" spans="1:11">
@@ -1135,86 +1199,62 @@
       <x:c r="E16" s="4"/>
       <x:c r="F16" s="4"/>
       <x:c r="G16" s="4"/>
-      <x:c r="H16" s="3"/>
-      <x:c r="I16" s="3"/>
-      <x:c r="J16" s="3"/>
-      <x:c r="K16" s="3"/>
-    </x:row>
-    <x:row r="17" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A17" s="11" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="B17" s="11" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C17" s="11" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="D17" s="11" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="E17" s="11" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="F17" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G17" s="11" t="s">
-        <x:v>17</x:v>
+      <x:c r="H16" s="4"/>
+      <x:c r="I16" s="4"/>
+      <x:c r="J16" s="4"/>
+      <x:c r="K16" s="4"/>
+    </x:row>
+    <x:row r="17" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A17" s="8" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B17" s="9"/>
+      <x:c r="C17" s="9"/>
+      <x:c r="D17" s="9"/>
+      <x:c r="E17" s="9"/>
+      <x:c r="F17" s="9"/>
+      <x:c r="G17" s="10" t="s">
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H17" s="3"/>
       <x:c r="I17" s="3"/>
       <x:c r="J17" s="3"/>
       <x:c r="K17" s="3"/>
     </x:row>
-    <x:row r="18" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A18" s="12" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="B18" s="12" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C18" s="12" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D18" s="12" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E18" s="12" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="F18" s="12" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="G18" s="12" t="s">
-        <x:v>56</x:v>
-      </x:c>
+    <x:row r="18" spans="1:11">
+      <x:c r="A18" s="4"/>
+      <x:c r="B18" s="4"/>
+      <x:c r="C18" s="4"/>
+      <x:c r="D18" s="4"/>
+      <x:c r="E18" s="4"/>
+      <x:c r="F18" s="4"/>
+      <x:c r="G18" s="4"/>
       <x:c r="H18" s="3"/>
       <x:c r="I18" s="3"/>
       <x:c r="J18" s="3"/>
       <x:c r="K18" s="3"/>
     </x:row>
-    <x:row r="19" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A19" s="12" t="s">
+    <x:row r="19" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A19" s="11" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="B19" s="12" t="s">
+      <x:c r="B19" s="11" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="C19" s="12" t="s">
+      <x:c r="C19" s="11" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="D19" s="12" t="s">
+      <x:c r="D19" s="11" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="E19" s="12" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="F19" s="12" t="s">
+      <x:c r="E19" s="11" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="G19" s="12" t="s">
-        <x:v>62</x:v>
+      <x:c r="F19" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G19" s="11" t="s">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="H19" s="3"/>
       <x:c r="I19" s="3"/>
@@ -1223,10 +1263,10 @@
     </x:row>
     <x:row r="20" spans="1:11" ht="30" customHeight="1">
       <x:c r="A20" s="12" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B20" s="12" t="s">
         <x:v>63</x:v>
-      </x:c>
-      <x:c r="B20" s="12" t="s">
-        <x:v>58</x:v>
       </x:c>
       <x:c r="C20" s="12" t="s">
         <x:v>64</x:v>
@@ -1235,13 +1275,13 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="E20" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F20" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="G20" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="H20" s="3"/>
       <x:c r="I20" s="3"/>
@@ -1249,61 +1289,85 @@
       <x:c r="K20" s="3"/>
     </x:row>
     <x:row r="21" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A21" s="13" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="B21" s="13" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C21" s="13" t="s">
+      <x:c r="A21" s="12" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="D21" s="13" t="s">
+      <x:c r="B21" s="12" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C21" s="12" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="E21" s="13" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="F21" s="13" t="s">
+      <x:c r="D21" s="12" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="G21" s="13" t="s">
+      <x:c r="E21" s="12" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="F21" s="12" t="s">
         <x:v>72</x:v>
+      </x:c>
+      <x:c r="G21" s="12" t="s">
+        <x:v>73</x:v>
       </x:c>
       <x:c r="H21" s="3"/>
       <x:c r="I21" s="3"/>
       <x:c r="J21" s="3"/>
       <x:c r="K21" s="3"/>
     </x:row>
-    <x:row r="22" spans="1:11">
-      <x:c r="A22" s="4"/>
-      <x:c r="B22" s="4"/>
-      <x:c r="C22" s="4"/>
-      <x:c r="D22" s="4"/>
-      <x:c r="E22" s="4"/>
-      <x:c r="F22" s="4"/>
-      <x:c r="G22" s="4"/>
-      <x:c r="H22" s="4"/>
-      <x:c r="I22" s="4"/>
-      <x:c r="J22" s="4"/>
-      <x:c r="K22" s="4"/>
-    </x:row>
-    <x:row r="23" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A23" s="8" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B23" s="9"/>
-      <x:c r="C23" s="9"/>
-      <x:c r="D23" s="9"/>
-      <x:c r="E23" s="9"/>
-      <x:c r="F23" s="9"/>
-      <x:c r="G23" s="9"/>
-      <x:c r="H23" s="9"/>
-      <x:c r="I23" s="9"/>
-      <x:c r="J23" s="9"/>
-      <x:c r="K23" s="10" t="s">
-        <x:v>73</x:v>
-      </x:c>
+    <x:row r="22" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A22" s="12" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B22" s="12" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C22" s="12" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="D22" s="12" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="E22" s="12" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="F22" s="12" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="G22" s="12" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="H22" s="3"/>
+      <x:c r="I22" s="3"/>
+      <x:c r="J22" s="3"/>
+      <x:c r="K22" s="3"/>
+    </x:row>
+    <x:row r="23" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A23" s="13" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B23" s="13" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C23" s="13" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D23" s="13" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="E23" s="13" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="F23" s="13" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="G23" s="13" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="H23" s="3"/>
+      <x:c r="I23" s="3"/>
+      <x:c r="J23" s="3"/>
+      <x:c r="K23" s="3"/>
     </x:row>
     <x:row r="24" spans="1:11">
       <x:c r="A24" s="4"/>
@@ -1318,74 +1382,104 @@
       <x:c r="J24" s="4"/>
       <x:c r="K24" s="4"/>
     </x:row>
-    <x:row r="25" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A25" s="11" t="s">
+    <x:row r="25" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A25" s="8" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B25" s="9"/>
+      <x:c r="C25" s="9"/>
+      <x:c r="D25" s="9"/>
+      <x:c r="E25" s="9"/>
+      <x:c r="F25" s="9"/>
+      <x:c r="G25" s="9"/>
+      <x:c r="H25" s="9"/>
+      <x:c r="I25" s="9"/>
+      <x:c r="J25" s="9"/>
+      <x:c r="K25" s="10" t="s">
+        <x:v>85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:11">
+      <x:c r="A26" s="4"/>
+      <x:c r="B26" s="4"/>
+      <x:c r="C26" s="4"/>
+      <x:c r="D26" s="4"/>
+      <x:c r="E26" s="4"/>
+      <x:c r="F26" s="4"/>
+      <x:c r="G26" s="4"/>
+      <x:c r="H26" s="4"/>
+      <x:c r="I26" s="4"/>
+      <x:c r="J26" s="4"/>
+      <x:c r="K26" s="4"/>
+    </x:row>
+    <x:row r="27" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A27" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B25" s="11" t="s">
+      <x:c r="B27" s="11" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C25" s="11" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="D25" s="11" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="E25" s="11" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="F25" s="11" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="G25" s="11" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="H25" s="11" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="I25" s="11" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="J25" s="11" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="K25" s="11" t="s">
-        <x:v>82</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A26" s="13" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="B26" s="13" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="C26" s="13" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="D26" s="13" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="E26" s="13" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="F26" s="13" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="G26" s="13" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="H26" s="13" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="I26" s="13" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="J26" s="13" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="K26" s="13" t="s">
-        <x:v>84</x:v>
+      <x:c r="C27" s="11" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="D27" s="11" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="E27" s="11" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="F27" s="11" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="G27" s="11" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="H27" s="11" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="I27" s="11" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="J27" s="11" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="K27" s="11" t="s">
+        <x:v>94</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A28" s="13" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B28" s="13" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C28" s="13" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D28" s="13" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="E28" s="13" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="F28" s="13" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="G28" s="13" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="H28" s="13" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="I28" s="13" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="J28" s="13" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="K28" s="13" t="s">
+        <x:v>96</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1393,8 +1487,8 @@
     <x:mergeCell ref="A1:E1"/>
     <x:mergeCell ref="F1:G1"/>
     <x:mergeCell ref="A7:F7"/>
-    <x:mergeCell ref="A15:F15"/>
-    <x:mergeCell ref="A23:J23"/>
+    <x:mergeCell ref="A17:F17"/>
+    <x:mergeCell ref="A25:J25"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/data/positions/Posição Consolidada - 5166121.xlsx
+++ b/data/positions/Posição Consolidada - 5166121.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 5166121 | 30/09/2026, 08:52</x:t>
+    <x:t>Conta: 5166121 | 13/10/2026, 11:10</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,13 +34,13 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>62,2%|Operações Compromissadas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 11.639.240,31</x:t>
-  </x:si>
-  <x:si>
-    <x:t>62,10%|Pós-Fixada</x:t>
+    <x:t>54,3%|Operações Compromissadas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 8.457.711,37</x:t>
+  </x:si>
+  <x:si>
+    <x:t>54,30%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -70,52 +70,73 @@
     <x:t>Valor líquido</x:t>
   </x:si>
   <x:si>
-    <x:t>14/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14/10/2026</x:t>
+    <x:t>23/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27/10/2026</x:t>
   </x:si>
   <x:si>
     <x:t>85,00% CDI</x:t>
   </x:si>
   <x:si>
-    <x:t>771.462,00</x:t>
+    <x:t>889.710,00</x:t>
   </x:si>
   <x:si>
     <x:t>0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.311.486,80</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.318.326,25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.316.787,37</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22/10/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.028.571,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.799.999,99</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.806.225,84</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.804.825,02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>937.500,00</x:t>
+    <x:t>R$ 1.423.536,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.431.545,71</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.429.743,52</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29/10/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.156.069,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.999.999,99</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.009.517,88</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.007.376,36</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30/10/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.420.454,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.499.999,99</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.510.813,44</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.508.380,41</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01/10/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05/11/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.145,00</x:t>
   </x:si>
   <x:si>
     <x:t>R$ 1.500.000,00</x:t>
@@ -127,67 +148,31 @@
     <x:t>R$ 1.503.517,49</x:t>
   </x:si>
   <x:si>
-    <x:t>23/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27/10/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.562.499,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.499.998,40</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.505.399,27</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.504.184,07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29/10/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.156.069,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.999.999,99</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.002.591,30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.002.008,26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30/10/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.420.454,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.499.999,99</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.502.158,95</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.501.673,18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>37,8%|Fundos de Investimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 7.085.739,96</x:t>
-  </x:si>
-  <x:si>
-    <x:t>37,80%|Fundos de Renda Fixa Pós-Fixado</x:t>
+    <x:t>07/10/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10/11/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>621.118,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.000.000,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.001.295,64</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.001.004,12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>45,7%|Fundos de Investimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 7.116.680,16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>45,60%|Fundos de Renda Fixa Pós-Fixado</x:t>
   </x:si>
   <x:si>
     <x:t>Data cota</x:t>
@@ -205,10 +190,10 @@
     <x:t>Safra DI Master FIRF Referenciado DI LP</x:t>
   </x:si>
   <x:si>
-    <x:t>29/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 275,61</x:t>
+    <x:t>13/10/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 276,87</x:t>
   </x:si>
   <x:si>
     <x:t>7.363,69</x:t>
@@ -217,61 +202,58 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.029.530,77</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.022.886,35</x:t>
+    <x:t>R$ 2.038.788,03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.030.060,73</x:t>
   </x:si>
   <x:si>
     <x:t>XP Bancos FIRF Referenciada DI CP RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1,95</x:t>
+    <x:t>R$ 1,96</x:t>
   </x:si>
   <x:si>
     <x:t>1.030.619,91</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.011.391,93</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.005.664,30</x:t>
+    <x:t>R$ 2.020.622,25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.014.911,45</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
   </x:si>
   <x:si>
-    <x:t>30/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.459,43</x:t>
+    <x:t>R$ 1.465,36</x:t>
   </x:si>
   <x:si>
     <x:t>1.390,64</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.029.548,24</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.022.899,89</x:t>
+    <x:t>R$ 2.037.784,61</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.029.283,08</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1,49</x:t>
+    <x:t>R$ 1,50</x:t>
   </x:si>
   <x:si>
     <x:t>680.719,86</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.015.269,02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.011.833,49</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 0,85</x:t>
+    <x:t>R$ 1.019.485,27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.015.101,09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 167,08</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -301,7 +283,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>0,85</x:t>
+    <x:t>167,08</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -849,7 +831,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K28"/>
+  <x:dimension ref="A1:K27"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="38.282054" style="0" customWidth="1"/>
@@ -909,13 +891,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>18724981.1202784</x:v>
+        <x:v>15574558.614787</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>18724980.2702784</x:v>
+        <x:v>15574391.534787</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>0.85</x:v>
+        <x:v>167.08</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
@@ -1082,179 +1064,177 @@
       </x:c>
       <x:c r="C12" s="12"/>
       <x:c r="D12" s="12" t="s">
-        <x:v>27</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E12" s="12" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="F12" s="12" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G12" s="12" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="H12" s="12" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="I12" s="12" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="J12" s="12" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="K12" s="3"/>
     </x:row>
     <x:row r="13" spans="1:11" ht="30" customHeight="1">
       <x:c r="A13" s="12"/>
       <x:c r="B13" s="12" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C13" s="12"/>
       <x:c r="D13" s="12" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E13" s="12" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="F13" s="12" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G13" s="12" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="H13" s="12" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="I13" s="12" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="J13" s="12" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="K13" s="3"/>
     </x:row>
     <x:row r="14" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A14" s="12"/>
-      <x:c r="B14" s="12" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C14" s="12"/>
-      <x:c r="D14" s="12" t="s">
+      <x:c r="A14" s="13"/>
+      <x:c r="B14" s="13" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="E14" s="12" t="s">
+      <x:c r="C14" s="13"/>
+      <x:c r="D14" s="13" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E14" s="13" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="F14" s="12" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="G14" s="12" t="s">
+      <x:c r="F14" s="13" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="G14" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="H14" s="12" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="I14" s="12" t="s">
+      <x:c r="H14" s="13" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="J14" s="12" t="s">
+      <x:c r="I14" s="13" t="s">
         <x:v>48</x:v>
       </x:c>
+      <x:c r="J14" s="13" t="s">
+        <x:v>49</x:v>
+      </x:c>
       <x:c r="K14" s="3"/>
     </x:row>
-    <x:row r="15" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A15" s="13"/>
-      <x:c r="B15" s="13" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C15" s="13"/>
-      <x:c r="D15" s="13" t="s">
+    <x:row r="15" spans="1:11">
+      <x:c r="A15" s="4"/>
+      <x:c r="B15" s="4"/>
+      <x:c r="C15" s="4"/>
+      <x:c r="D15" s="4"/>
+      <x:c r="E15" s="4"/>
+      <x:c r="F15" s="4"/>
+      <x:c r="G15" s="4"/>
+      <x:c r="H15" s="4"/>
+      <x:c r="I15" s="4"/>
+      <x:c r="J15" s="4"/>
+      <x:c r="K15" s="4"/>
+    </x:row>
+    <x:row r="16" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A16" s="8" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="E15" s="13" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F15" s="13" t="s">
+      <x:c r="B16" s="9"/>
+      <x:c r="C16" s="9"/>
+      <x:c r="D16" s="9"/>
+      <x:c r="E16" s="9"/>
+      <x:c r="F16" s="9"/>
+      <x:c r="G16" s="10" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="G15" s="13" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H15" s="13" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="I15" s="13" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="J15" s="13" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="K15" s="3"/>
-    </x:row>
-    <x:row r="16" spans="1:11">
-      <x:c r="A16" s="4"/>
-      <x:c r="B16" s="4"/>
-      <x:c r="C16" s="4"/>
-      <x:c r="D16" s="4"/>
-      <x:c r="E16" s="4"/>
-      <x:c r="F16" s="4"/>
-      <x:c r="G16" s="4"/>
-      <x:c r="H16" s="4"/>
-      <x:c r="I16" s="4"/>
-      <x:c r="J16" s="4"/>
-      <x:c r="K16" s="4"/>
-    </x:row>
-    <x:row r="17" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A17" s="8" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="B17" s="9"/>
-      <x:c r="C17" s="9"/>
-      <x:c r="D17" s="9"/>
-      <x:c r="E17" s="9"/>
-      <x:c r="F17" s="9"/>
-      <x:c r="G17" s="10" t="s">
-        <x:v>56</x:v>
-      </x:c>
+      <x:c r="H16" s="3"/>
+      <x:c r="I16" s="3"/>
+      <x:c r="J16" s="3"/>
+      <x:c r="K16" s="3"/>
+    </x:row>
+    <x:row r="17" spans="1:11">
+      <x:c r="A17" s="4"/>
+      <x:c r="B17" s="4"/>
+      <x:c r="C17" s="4"/>
+      <x:c r="D17" s="4"/>
+      <x:c r="E17" s="4"/>
+      <x:c r="F17" s="4"/>
+      <x:c r="G17" s="4"/>
       <x:c r="H17" s="3"/>
       <x:c r="I17" s="3"/>
       <x:c r="J17" s="3"/>
       <x:c r="K17" s="3"/>
     </x:row>
-    <x:row r="18" spans="1:11">
-      <x:c r="A18" s="4"/>
-      <x:c r="B18" s="4"/>
-      <x:c r="C18" s="4"/>
-      <x:c r="D18" s="4"/>
-      <x:c r="E18" s="4"/>
-      <x:c r="F18" s="4"/>
-      <x:c r="G18" s="4"/>
+    <x:row r="18" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A18" s="11" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B18" s="11" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C18" s="11" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="D18" s="11" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E18" s="11" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F18" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G18" s="11" t="s">
+        <x:v>17</x:v>
+      </x:c>
       <x:c r="H18" s="3"/>
       <x:c r="I18" s="3"/>
       <x:c r="J18" s="3"/>
       <x:c r="K18" s="3"/>
     </x:row>
-    <x:row r="19" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A19" s="11" t="s">
+    <x:row r="19" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A19" s="12" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="B19" s="11" t="s">
+      <x:c r="B19" s="12" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="C19" s="11" t="s">
+      <x:c r="C19" s="12" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="D19" s="11" t="s">
+      <x:c r="D19" s="12" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="E19" s="11" t="s">
+      <x:c r="E19" s="12" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="F19" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G19" s="11" t="s">
-        <x:v>17</x:v>
+      <x:c r="F19" s="12" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="G19" s="12" t="s">
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H19" s="3"/>
       <x:c r="I19" s="3"/>
@@ -1263,19 +1243,19 @@
     </x:row>
     <x:row r="20" spans="1:11" ht="30" customHeight="1">
       <x:c r="A20" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B20" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C20" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D20" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E20" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F20" s="12" t="s">
         <x:v>67</x:v>
@@ -1293,7 +1273,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B21" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C21" s="12" t="s">
         <x:v>70</x:v>
@@ -1302,7 +1282,7 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="E21" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F21" s="12" t="s">
         <x:v>72</x:v>
@@ -1316,170 +1296,143 @@
       <x:c r="K21" s="3"/>
     </x:row>
     <x:row r="22" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A22" s="12" t="s">
+      <x:c r="A22" s="13" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="B22" s="12" t="s">
+      <x:c r="B22" s="13" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C22" s="13" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="C22" s="12" t="s">
+      <x:c r="D22" s="13" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="D22" s="12" t="s">
+      <x:c r="E22" s="13" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="F22" s="13" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="E22" s="12" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="F22" s="12" t="s">
+      <x:c r="G22" s="13" t="s">
         <x:v>78</x:v>
-      </x:c>
-      <x:c r="G22" s="12" t="s">
-        <x:v>79</x:v>
       </x:c>
       <x:c r="H22" s="3"/>
       <x:c r="I22" s="3"/>
       <x:c r="J22" s="3"/>
       <x:c r="K22" s="3"/>
     </x:row>
-    <x:row r="23" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A23" s="13" t="s">
+    <x:row r="23" spans="1:11">
+      <x:c r="A23" s="4"/>
+      <x:c r="B23" s="4"/>
+      <x:c r="C23" s="4"/>
+      <x:c r="D23" s="4"/>
+      <x:c r="E23" s="4"/>
+      <x:c r="F23" s="4"/>
+      <x:c r="G23" s="4"/>
+      <x:c r="H23" s="4"/>
+      <x:c r="I23" s="4"/>
+      <x:c r="J23" s="4"/>
+      <x:c r="K23" s="4"/>
+    </x:row>
+    <x:row r="24" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A24" s="8" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B24" s="9"/>
+      <x:c r="C24" s="9"/>
+      <x:c r="D24" s="9"/>
+      <x:c r="E24" s="9"/>
+      <x:c r="F24" s="9"/>
+      <x:c r="G24" s="9"/>
+      <x:c r="H24" s="9"/>
+      <x:c r="I24" s="9"/>
+      <x:c r="J24" s="9"/>
+      <x:c r="K24" s="10" t="s">
+        <x:v>79</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:11">
+      <x:c r="A25" s="4"/>
+      <x:c r="B25" s="4"/>
+      <x:c r="C25" s="4"/>
+      <x:c r="D25" s="4"/>
+      <x:c r="E25" s="4"/>
+      <x:c r="F25" s="4"/>
+      <x:c r="G25" s="4"/>
+      <x:c r="H25" s="4"/>
+      <x:c r="I25" s="4"/>
+      <x:c r="J25" s="4"/>
+      <x:c r="K25" s="4"/>
+    </x:row>
+    <x:row r="26" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A26" s="11" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B26" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C26" s="11" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="B23" s="13" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="C23" s="13" t="s">
+      <x:c r="D26" s="11" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="D23" s="13" t="s">
+      <x:c r="E26" s="11" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="E23" s="13" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="F23" s="13" t="s">
+      <x:c r="F26" s="11" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="G23" s="13" t="s">
+      <x:c r="G26" s="11" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="H23" s="3"/>
-      <x:c r="I23" s="3"/>
-      <x:c r="J23" s="3"/>
-      <x:c r="K23" s="3"/>
-    </x:row>
-    <x:row r="24" spans="1:11">
-      <x:c r="A24" s="4"/>
-      <x:c r="B24" s="4"/>
-      <x:c r="C24" s="4"/>
-      <x:c r="D24" s="4"/>
-      <x:c r="E24" s="4"/>
-      <x:c r="F24" s="4"/>
-      <x:c r="G24" s="4"/>
-      <x:c r="H24" s="4"/>
-      <x:c r="I24" s="4"/>
-      <x:c r="J24" s="4"/>
-      <x:c r="K24" s="4"/>
-    </x:row>
-    <x:row r="25" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A25" s="8" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B25" s="9"/>
-      <x:c r="C25" s="9"/>
-      <x:c r="D25" s="9"/>
-      <x:c r="E25" s="9"/>
-      <x:c r="F25" s="9"/>
-      <x:c r="G25" s="9"/>
-      <x:c r="H25" s="9"/>
-      <x:c r="I25" s="9"/>
-      <x:c r="J25" s="9"/>
-      <x:c r="K25" s="10" t="s">
+      <x:c r="H26" s="11" t="s">
         <x:v>85</x:v>
       </x:c>
-    </x:row>
-    <x:row r="26" spans="1:11">
-      <x:c r="A26" s="4"/>
-      <x:c r="B26" s="4"/>
-      <x:c r="C26" s="4"/>
-      <x:c r="D26" s="4"/>
-      <x:c r="E26" s="4"/>
-      <x:c r="F26" s="4"/>
-      <x:c r="G26" s="4"/>
-      <x:c r="H26" s="4"/>
-      <x:c r="I26" s="4"/>
-      <x:c r="J26" s="4"/>
-      <x:c r="K26" s="4"/>
-    </x:row>
-    <x:row r="27" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A27" s="11" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B27" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C27" s="11" t="s">
+      <x:c r="I26" s="11" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="D27" s="11" t="s">
+      <x:c r="J26" s="11" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="E27" s="11" t="s">
+      <x:c r="K26" s="11" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="F27" s="11" t="s">
+    </x:row>
+    <x:row r="27" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A27" s="13" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="G27" s="11" t="s">
+      <x:c r="B27" s="13" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="H27" s="11" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="I27" s="11" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="J27" s="11" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="K27" s="11" t="s">
-        <x:v>94</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A28" s="13" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="B28" s="13" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="C28" s="13" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="D28" s="13" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="E28" s="13" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="F28" s="13" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="G28" s="13" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="H28" s="13" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="I28" s="13" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="J28" s="13" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="K28" s="13" t="s">
-        <x:v>96</x:v>
+      <x:c r="C27" s="13" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D27" s="13" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="E27" s="13" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="F27" s="13" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="G27" s="13" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="H27" s="13" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="I27" s="13" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="J27" s="13" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="K27" s="13" t="s">
+        <x:v>90</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1487,8 +1440,8 @@
     <x:mergeCell ref="A1:E1"/>
     <x:mergeCell ref="F1:G1"/>
     <x:mergeCell ref="A7:F7"/>
-    <x:mergeCell ref="A17:F17"/>
-    <x:mergeCell ref="A25:J25"/>
+    <x:mergeCell ref="A16:F16"/>
+    <x:mergeCell ref="A24:J24"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/data/positions/Posição Consolidada - 5166121.xlsx
+++ b/data/positions/Posição Consolidada - 5166121.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 5166121 | 13/10/2026, 11:10</x:t>
+    <x:t>Conta: 5166121 | 14/10/2026, 08:49</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>54,3%|Operações Compromissadas</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 8.457.711,37</x:t>
+    <x:t>R$ 8.461.362,55</x:t>
   </x:si>
   <x:si>
     <x:t>54,30%|Pós-Fixada</x:t>
@@ -88,10 +88,10 @@
     <x:t>R$ 1.423.536,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.431.545,71</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.429.743,52</x:t>
+    <x:t>R$ 1.432.163,70</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.430.222,47</x:t>
   </x:si>
   <x:si>
     <x:t>25/09/2026</x:t>
@@ -106,10 +106,10 @@
     <x:t>R$ 1.999.999,99</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.009.517,88</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.007.376,36</x:t>
+    <x:t>R$ 2.010.385,38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.008.048,67</x:t>
   </x:si>
   <x:si>
     <x:t>28/09/2026</x:t>
@@ -124,10 +124,10 @@
     <x:t>R$ 2.499.999,99</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.510.813,44</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.508.380,41</x:t>
+    <x:t>R$ 2.511.897,36</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.509.220,45</x:t>
   </x:si>
   <x:si>
     <x:t>01/10/2026</x:t>
@@ -142,10 +142,10 @@
     <x:t>R$ 1.500.000,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.504.538,70</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.503.517,49</x:t>
+    <x:t>R$ 1.505.188,21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.504.020,86</x:t>
   </x:si>
   <x:si>
     <x:t>07/10/2026</x:t>
@@ -160,10 +160,10 @@
     <x:t>R$ 1.000.000,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.001.295,64</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.001.004,12</x:t>
+    <x:t>R$ 1.001.727,90</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.001.339,12</x:t>
   </x:si>
   <x:si>
     <x:t>45,7%|Fundos de Investimento</x:t>
@@ -253,7 +253,10 @@
     <x:t>R$ 1.015.101,09</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 167,08</x:t>
+    <x:t>0,01%|Saldo projetado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.096,58</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -287,6 +290,9 @@
   </x:si>
   <x:si>
     <x:t>0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1929,5</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -891,16 +897,16 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>15574558.614787</x:v>
+        <x:v>15580139.290488</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>15574391.534787</x:v>
+        <x:v>15578042.710488</x:v>
       </x:c>
       <x:c r="C4" s="7">
         <x:v>167.08</x:v>
       </x:c>
       <x:c r="D4" s="7">
-        <x:v>0</x:v>
+        <x:v>1929.5</x:v>
       </x:c>
       <x:c r="E4" s="4"/>
       <x:c r="F4" s="4"/>
@@ -1337,7 +1343,7 @@
     </x:row>
     <x:row r="24" spans="1:11" ht="45" customHeight="1">
       <x:c r="A24" s="8" t="s">
-        <x:v>5</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B24" s="9"/>
       <x:c r="C24" s="9"/>
@@ -1349,7 +1355,7 @@
       <x:c r="I24" s="9"/>
       <x:c r="J24" s="9"/>
       <x:c r="K24" s="10" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:11">
@@ -1373,66 +1379,66 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C26" s="11" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D26" s="11" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E26" s="11" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="F26" s="11" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="G26" s="11" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="H26" s="11" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="I26" s="11" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="J26" s="11" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="K26" s="11" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:11" ht="30" customHeight="1">
       <x:c r="A27" s="13" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B27" s="13" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C27" s="13" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D27" s="13" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E27" s="13" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="F27" s="13" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="G27" s="13" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="H27" s="13" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="I27" s="13" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="J27" s="13" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="K27" s="13" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/data/positions/Posição Consolidada - 5166121.xlsx
+++ b/data/positions/Posição Consolidada - 5166121.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 5166121 | 14/10/2026, 08:49</x:t>
+    <x:t>Conta: 5166121 | 27/10/2026, 19:01</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,13 +34,13 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>54,3%|Operações Compromissadas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 8.461.362,55</x:t>
-  </x:si>
-  <x:si>
-    <x:t>54,30%|Pós-Fixada</x:t>
+    <x:t>11,1%|Renda Fixa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.010.824,76</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11,10%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -70,193 +70,217 @@
     <x:t>Valor líquido</x:t>
   </x:si>
   <x:si>
-    <x:t>23/09/2026</x:t>
+    <x:t>LCA BNDES - JUN/2028</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15/10/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27/06/2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30/06/2028</x:t>
+  </x:si>
+  <x:si>
+    <x:t>80,50% CDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>170,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.004.259,95</x:t>
+  </x:si>
+  <x:si>
+    <x:t>32,6%|Operações Compromissadas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.874.111,08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>32,50%|Pós-Fixada</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30/10/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>85,00% CDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>480.727,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 846.079,84</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 853.414,89</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 851.764,50</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01/10/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05/11/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.145,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.500.000,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.511.046,40</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.508.560,96</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07/10/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10/11/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>621.117,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 999.998,39</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.005.625,01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.004.359,02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21/10/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25/11/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>637.579,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.001.000,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.002.729,42</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.002.340,30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23/10/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27/11/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>914.634,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.501.295,37</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.501.003,91</x:t>
+  </x:si>
+  <x:si>
+    <x:t>56,3%|Fundos de Investimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 10.159.631,83</x:t>
+  </x:si>
+  <x:si>
+    <x:t>56,30%|Fundos de Renda Fixa Pós-Fixado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Data cota</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Valor cota</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Qtd. cotas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Em cotização</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Safra DI Master FIRF Referenciado DI LP</x:t>
   </x:si>
   <x:si>
     <x:t>27/10/2026</x:t>
   </x:si>
   <x:si>
-    <x:t>85,00% CDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>889.710,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.423.536,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.432.163,70</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.430.222,47</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29/10/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.156.069,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.999.999,99</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.010.385,38</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.008.048,67</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30/10/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.420.454,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.499.999,99</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.511.897,36</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.509.220,45</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01/10/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05/11/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.145,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.500.000,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.505.188,21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.504.020,86</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07/10/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10/11/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>621.118,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.000.000,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.001.727,90</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.001.339,12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>45,7%|Fundos de Investimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 7.116.680,16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>45,60%|Fundos de Renda Fixa Pós-Fixado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Data cota</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Valor cota</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Qtd. cotas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Em cotização</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Safra DI Master FIRF Referenciado DI LP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13/10/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 276,87</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7.363,69</x:t>
+    <x:t>R$ 278,22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.972,10</x:t>
   </x:si>
   <x:si>
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.038.788,03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.030.060,73</x:t>
+    <x:t>R$ 3.052.610,53</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 3.038.951,85</x:t>
   </x:si>
   <x:si>
     <x:t>XP Bancos FIRF Referenciada DI CP RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1,96</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.030.619,91</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.020.622,25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.014.911,45</x:t>
+    <x:t>R$ 1,97</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.538.134,23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 3.031.240,66</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 3.022.067,25</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.465,36</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.390,64</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.037.784,61</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.029.283,08</x:t>
+    <x:t>R$ 1.472,21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2.072,46</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 3.051.079,63</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 3.037.833,32</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1,50</x:t>
+    <x:t>R$ 1,51</x:t>
   </x:si>
   <x:si>
     <x:t>680.719,86</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.019.485,27</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.015.101,09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0,01%|Saldo projetado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.096,58</x:t>
+    <x:t>R$ 1.024.701,01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.019.143,29</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 837,22</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -286,13 +310,10 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>167,08</x:t>
+    <x:t>837,22</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1929,5</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -534,11 +555,11 @@
       <x:alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -837,7 +858,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K27"/>
+  <x:dimension ref="A1:K32"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="38.282054" style="0" customWidth="1"/>
@@ -897,16 +918,16 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>15580139.290488</x:v>
+        <x:v>18045404.8930348</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>15578042.710488</x:v>
+        <x:v>18044567.6730348</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>167.08</x:v>
+        <x:v>837.22</x:v>
       </x:c>
       <x:c r="D4" s="7">
-        <x:v>1929.5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E4" s="4"/>
       <x:c r="F4" s="4"/>
@@ -1006,448 +1027,558 @@
       <x:c r="K9" s="3"/>
     </x:row>
     <x:row r="10" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A10" s="12"/>
+      <x:c r="A10" s="12" t="s">
+        <x:v>18</x:v>
+      </x:c>
       <x:c r="B10" s="12" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C10" s="12"/>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C10" s="12" t="s">
+        <x:v>20</x:v>
+      </x:c>
       <x:c r="D10" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E10" s="12" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F10" s="12" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G10" s="12" t="s">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H10" s="12" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="I10" s="12" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="J10" s="12" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="K10" s="3"/>
+    </x:row>
+    <x:row r="11" spans="1:11">
+      <x:c r="A11" s="4"/>
+      <x:c r="B11" s="4"/>
+      <x:c r="C11" s="4"/>
+      <x:c r="D11" s="4"/>
+      <x:c r="E11" s="4"/>
+      <x:c r="F11" s="4"/>
+      <x:c r="G11" s="4"/>
+      <x:c r="H11" s="4"/>
+      <x:c r="I11" s="4"/>
+      <x:c r="J11" s="4"/>
+      <x:c r="K11" s="4"/>
+    </x:row>
+    <x:row r="12" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A12" s="8" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B12" s="9"/>
+      <x:c r="C12" s="9"/>
+      <x:c r="D12" s="9"/>
+      <x:c r="E12" s="9"/>
+      <x:c r="F12" s="9"/>
+      <x:c r="G12" s="10" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="H12" s="3"/>
+      <x:c r="I12" s="3"/>
+      <x:c r="J12" s="3"/>
+      <x:c r="K12" s="3"/>
+    </x:row>
+    <x:row r="13" spans="1:11">
+      <x:c r="A13" s="4"/>
+      <x:c r="B13" s="4"/>
+      <x:c r="C13" s="4"/>
+      <x:c r="D13" s="4"/>
+      <x:c r="E13" s="4"/>
+      <x:c r="F13" s="4"/>
+      <x:c r="G13" s="4"/>
+      <x:c r="H13" s="3"/>
+      <x:c r="I13" s="3"/>
+      <x:c r="J13" s="3"/>
+      <x:c r="K13" s="3"/>
+    </x:row>
+    <x:row r="14" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A14" s="11" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B14" s="11" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C14" s="11" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D14" s="11" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E14" s="11" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F14" s="11" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G14" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H14" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I14" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J14" s="11" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K14" s="3"/>
+    </x:row>
+    <x:row r="15" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A15" s="13"/>
+      <x:c r="B15" s="13" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C15" s="13"/>
+      <x:c r="D15" s="13" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E15" s="13" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F15" s="13" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G15" s="13" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="J10" s="12" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="K10" s="3"/>
-    </x:row>
-    <x:row r="11" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A11" s="12"/>
-      <x:c r="B11" s="12" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C11" s="12"/>
-      <x:c r="D11" s="12" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E11" s="12" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F11" s="12" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="G11" s="12" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H11" s="12" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="I11" s="12" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="J11" s="12" t="s">
+      <x:c r="H15" s="13" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="I15" s="13" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="J15" s="13" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="K15" s="3"/>
+    </x:row>
+    <x:row r="16" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A16" s="13"/>
+      <x:c r="B16" s="13" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C16" s="13"/>
+      <x:c r="D16" s="13" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E16" s="13" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="K11" s="3"/>
-    </x:row>
-    <x:row r="12" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A12" s="12"/>
-      <x:c r="B12" s="12" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C12" s="12"/>
-      <x:c r="D12" s="12" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E12" s="12" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F12" s="12" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="G12" s="12" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H12" s="12" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="I12" s="12" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="J12" s="12" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="K12" s="3"/>
-    </x:row>
-    <x:row r="13" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A13" s="12"/>
-      <x:c r="B13" s="12" t="s">
+      <x:c r="F16" s="13" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C13" s="12"/>
-      <x:c r="D13" s="12" t="s">
+      <x:c r="G16" s="13" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H16" s="13" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="E13" s="12" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F13" s="12" t="s">
+      <x:c r="I16" s="13" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="G13" s="12" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H13" s="12" t="s">
+      <x:c r="J16" s="13" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="I13" s="12" t="s">
+      <x:c r="K16" s="3"/>
+    </x:row>
+    <x:row r="17" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A17" s="13"/>
+      <x:c r="B17" s="13" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="J13" s="12" t="s">
+      <x:c r="C17" s="13"/>
+      <x:c r="D17" s="13" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="K13" s="3"/>
-    </x:row>
-    <x:row r="14" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A14" s="13"/>
-      <x:c r="B14" s="13" t="s">
+      <x:c r="E17" s="13" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F17" s="13" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C14" s="13"/>
-      <x:c r="D14" s="13" t="s">
+      <x:c r="G17" s="13" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H17" s="13" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="E14" s="13" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F14" s="13" t="s">
+      <x:c r="I17" s="13" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="G14" s="13" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H14" s="13" t="s">
+      <x:c r="J17" s="13" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="I14" s="13" t="s">
+      <x:c r="K17" s="3"/>
+    </x:row>
+    <x:row r="18" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A18" s="13"/>
+      <x:c r="B18" s="13" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="J14" s="13" t="s">
+      <x:c r="C18" s="13"/>
+      <x:c r="D18" s="13" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="K14" s="3"/>
-    </x:row>
-    <x:row r="15" spans="1:11">
-      <x:c r="A15" s="4"/>
-      <x:c r="B15" s="4"/>
-      <x:c r="C15" s="4"/>
-      <x:c r="D15" s="4"/>
-      <x:c r="E15" s="4"/>
-      <x:c r="F15" s="4"/>
-      <x:c r="G15" s="4"/>
-      <x:c r="H15" s="4"/>
-      <x:c r="I15" s="4"/>
-      <x:c r="J15" s="4"/>
-      <x:c r="K15" s="4"/>
-    </x:row>
-    <x:row r="16" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A16" s="8" t="s">
+      <x:c r="E18" s="13" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F18" s="13" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="B16" s="9"/>
-      <x:c r="C16" s="9"/>
-      <x:c r="D16" s="9"/>
-      <x:c r="E16" s="9"/>
-      <x:c r="F16" s="9"/>
-      <x:c r="G16" s="10" t="s">
+      <x:c r="G18" s="13" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H18" s="13" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="H16" s="3"/>
-      <x:c r="I16" s="3"/>
-      <x:c r="J16" s="3"/>
-      <x:c r="K16" s="3"/>
-    </x:row>
-    <x:row r="17" spans="1:11">
-      <x:c r="A17" s="4"/>
-      <x:c r="B17" s="4"/>
-      <x:c r="C17" s="4"/>
-      <x:c r="D17" s="4"/>
-      <x:c r="E17" s="4"/>
-      <x:c r="F17" s="4"/>
-      <x:c r="G17" s="4"/>
-      <x:c r="H17" s="3"/>
-      <x:c r="I17" s="3"/>
-      <x:c r="J17" s="3"/>
-      <x:c r="K17" s="3"/>
-    </x:row>
-    <x:row r="18" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A18" s="11" t="s">
+      <x:c r="I18" s="13" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="B18" s="11" t="s">
+      <x:c r="J18" s="13" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="C18" s="11" t="s">
+      <x:c r="K18" s="3"/>
+    </x:row>
+    <x:row r="19" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A19" s="12"/>
+      <x:c r="B19" s="12" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="D18" s="11" t="s">
+      <x:c r="C19" s="12"/>
+      <x:c r="D19" s="12" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="E18" s="11" t="s">
+      <x:c r="E19" s="12" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F19" s="12" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="F18" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G18" s="11" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H18" s="3"/>
-      <x:c r="I18" s="3"/>
-      <x:c r="J18" s="3"/>
-      <x:c r="K18" s="3"/>
-    </x:row>
-    <x:row r="19" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A19" s="12" t="s">
+      <x:c r="G19" s="12" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H19" s="12" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I19" s="12" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="B19" s="12" t="s">
+      <x:c r="J19" s="12" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="C19" s="12" t="s">
+      <x:c r="K19" s="3"/>
+    </x:row>
+    <x:row r="20" spans="1:11">
+      <x:c r="A20" s="4"/>
+      <x:c r="B20" s="4"/>
+      <x:c r="C20" s="4"/>
+      <x:c r="D20" s="4"/>
+      <x:c r="E20" s="4"/>
+      <x:c r="F20" s="4"/>
+      <x:c r="G20" s="4"/>
+      <x:c r="H20" s="4"/>
+      <x:c r="I20" s="4"/>
+      <x:c r="J20" s="4"/>
+      <x:c r="K20" s="4"/>
+    </x:row>
+    <x:row r="21" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A21" s="8" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="D19" s="12" t="s">
+      <x:c r="B21" s="9"/>
+      <x:c r="C21" s="9"/>
+      <x:c r="D21" s="9"/>
+      <x:c r="E21" s="9"/>
+      <x:c r="F21" s="9"/>
+      <x:c r="G21" s="10" t="s">
         <x:v>60</x:v>
-      </x:c>
-      <x:c r="E19" s="12" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="F19" s="12" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="G19" s="12" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="H19" s="3"/>
-      <x:c r="I19" s="3"/>
-      <x:c r="J19" s="3"/>
-      <x:c r="K19" s="3"/>
-    </x:row>
-    <x:row r="20" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A20" s="12" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="B20" s="12" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C20" s="12" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="D20" s="12" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E20" s="12" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="F20" s="12" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="G20" s="12" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="H20" s="3"/>
-      <x:c r="I20" s="3"/>
-      <x:c r="J20" s="3"/>
-      <x:c r="K20" s="3"/>
-    </x:row>
-    <x:row r="21" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A21" s="12" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="B21" s="12" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C21" s="12" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="D21" s="12" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="E21" s="12" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="F21" s="12" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="G21" s="12" t="s">
-        <x:v>73</x:v>
       </x:c>
       <x:c r="H21" s="3"/>
       <x:c r="I21" s="3"/>
       <x:c r="J21" s="3"/>
       <x:c r="K21" s="3"/>
     </x:row>
-    <x:row r="22" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A22" s="13" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="B22" s="13" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C22" s="13" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="D22" s="13" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="E22" s="13" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="F22" s="13" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="G22" s="13" t="s">
-        <x:v>78</x:v>
-      </x:c>
+    <x:row r="22" spans="1:11">
+      <x:c r="A22" s="4"/>
+      <x:c r="B22" s="4"/>
+      <x:c r="C22" s="4"/>
+      <x:c r="D22" s="4"/>
+      <x:c r="E22" s="4"/>
+      <x:c r="F22" s="4"/>
+      <x:c r="G22" s="4"/>
       <x:c r="H22" s="3"/>
       <x:c r="I22" s="3"/>
       <x:c r="J22" s="3"/>
       <x:c r="K22" s="3"/>
     </x:row>
-    <x:row r="23" spans="1:11">
-      <x:c r="A23" s="4"/>
-      <x:c r="B23" s="4"/>
-      <x:c r="C23" s="4"/>
-      <x:c r="D23" s="4"/>
-      <x:c r="E23" s="4"/>
-      <x:c r="F23" s="4"/>
-      <x:c r="G23" s="4"/>
-      <x:c r="H23" s="4"/>
-      <x:c r="I23" s="4"/>
-      <x:c r="J23" s="4"/>
-      <x:c r="K23" s="4"/>
-    </x:row>
-    <x:row r="24" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A24" s="8" t="s">
+    <x:row r="23" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A23" s="11" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B23" s="11" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C23" s="11" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="D23" s="11" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="E23" s="11" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="F23" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G23" s="11" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H23" s="3"/>
+      <x:c r="I23" s="3"/>
+      <x:c r="J23" s="3"/>
+      <x:c r="K23" s="3"/>
+    </x:row>
+    <x:row r="24" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A24" s="13" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B24" s="13" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C24" s="13" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D24" s="13" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="E24" s="13" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="F24" s="13" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="G24" s="13" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="H24" s="3"/>
+      <x:c r="I24" s="3"/>
+      <x:c r="J24" s="3"/>
+      <x:c r="K24" s="3"/>
+    </x:row>
+    <x:row r="25" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A25" s="13" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B25" s="13" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C25" s="13" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="D25" s="13" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="E25" s="13" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="F25" s="13" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="G25" s="13" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H25" s="3"/>
+      <x:c r="I25" s="3"/>
+      <x:c r="J25" s="3"/>
+      <x:c r="K25" s="3"/>
+    </x:row>
+    <x:row r="26" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A26" s="13" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="B26" s="13" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C26" s="13" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="B24" s="9"/>
-      <x:c r="C24" s="9"/>
-      <x:c r="D24" s="9"/>
-      <x:c r="E24" s="9"/>
-      <x:c r="F24" s="9"/>
-      <x:c r="G24" s="9"/>
-      <x:c r="H24" s="9"/>
-      <x:c r="I24" s="9"/>
-      <x:c r="J24" s="9"/>
-      <x:c r="K24" s="10" t="s">
+      <x:c r="D26" s="13" t="s">
         <x:v>80</x:v>
       </x:c>
-    </x:row>
-    <x:row r="25" spans="1:11">
-      <x:c r="A25" s="4"/>
-      <x:c r="B25" s="4"/>
-      <x:c r="C25" s="4"/>
-      <x:c r="D25" s="4"/>
-      <x:c r="E25" s="4"/>
-      <x:c r="F25" s="4"/>
-      <x:c r="G25" s="4"/>
-      <x:c r="H25" s="4"/>
-      <x:c r="I25" s="4"/>
-      <x:c r="J25" s="4"/>
-      <x:c r="K25" s="4"/>
-    </x:row>
-    <x:row r="26" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A26" s="11" t="s">
+      <x:c r="E26" s="13" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="F26" s="13" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="G26" s="13" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="H26" s="3"/>
+      <x:c r="I26" s="3"/>
+      <x:c r="J26" s="3"/>
+      <x:c r="K26" s="3"/>
+    </x:row>
+    <x:row r="27" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A27" s="12" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B27" s="12" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C27" s="12" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="D27" s="12" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="E27" s="12" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="F27" s="12" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="G27" s="12" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="H27" s="3"/>
+      <x:c r="I27" s="3"/>
+      <x:c r="J27" s="3"/>
+      <x:c r="K27" s="3"/>
+    </x:row>
+    <x:row r="28" spans="1:11">
+      <x:c r="A28" s="4"/>
+      <x:c r="B28" s="4"/>
+      <x:c r="C28" s="4"/>
+      <x:c r="D28" s="4"/>
+      <x:c r="E28" s="4"/>
+      <x:c r="F28" s="4"/>
+      <x:c r="G28" s="4"/>
+      <x:c r="H28" s="4"/>
+      <x:c r="I28" s="4"/>
+      <x:c r="J28" s="4"/>
+      <x:c r="K28" s="4"/>
+    </x:row>
+    <x:row r="29" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A29" s="8" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B29" s="9"/>
+      <x:c r="C29" s="9"/>
+      <x:c r="D29" s="9"/>
+      <x:c r="E29" s="9"/>
+      <x:c r="F29" s="9"/>
+      <x:c r="G29" s="9"/>
+      <x:c r="H29" s="9"/>
+      <x:c r="I29" s="9"/>
+      <x:c r="J29" s="9"/>
+      <x:c r="K29" s="10" t="s">
+        <x:v>88</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:11">
+      <x:c r="A30" s="4"/>
+      <x:c r="B30" s="4"/>
+      <x:c r="C30" s="4"/>
+      <x:c r="D30" s="4"/>
+      <x:c r="E30" s="4"/>
+      <x:c r="F30" s="4"/>
+      <x:c r="G30" s="4"/>
+      <x:c r="H30" s="4"/>
+      <x:c r="I30" s="4"/>
+      <x:c r="J30" s="4"/>
+      <x:c r="K30" s="4"/>
+    </x:row>
+    <x:row r="31" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A31" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B26" s="11" t="s">
+      <x:c r="B31" s="11" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C26" s="11" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D26" s="11" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="E26" s="11" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="F26" s="11" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="G26" s="11" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="H26" s="11" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="I26" s="11" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="J26" s="11" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="K26" s="11" t="s">
+      <x:c r="C31" s="11" t="s">
         <x:v>89</x:v>
       </x:c>
-    </x:row>
-    <x:row r="27" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A27" s="13" t="s">
+      <x:c r="D31" s="11" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="B27" s="13" t="s">
+      <x:c r="E31" s="11" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="C27" s="13" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D27" s="13" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="E27" s="13" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="F27" s="13" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="G27" s="13" t="s">
+      <x:c r="F31" s="11" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="H27" s="13" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="I27" s="13" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="J27" s="13" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="K27" s="13" t="s">
-        <x:v>91</x:v>
+      <x:c r="G31" s="11" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="H31" s="11" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="I31" s="11" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="J31" s="11" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="K31" s="11" t="s">
+        <x:v>97</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A32" s="12" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="B32" s="12" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C32" s="12" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D32" s="12" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="E32" s="12" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="F32" s="12" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="G32" s="12" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="H32" s="12" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="I32" s="12" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="J32" s="12" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="K32" s="12" t="s">
+        <x:v>99</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:mergeCells count="5">
+  <x:mergeCells count="6">
     <x:mergeCell ref="A1:E1"/>
     <x:mergeCell ref="F1:G1"/>
     <x:mergeCell ref="A7:F7"/>
-    <x:mergeCell ref="A16:F16"/>
-    <x:mergeCell ref="A24:J24"/>
+    <x:mergeCell ref="A12:F12"/>
+    <x:mergeCell ref="A21:F21"/>
+    <x:mergeCell ref="A29:J29"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/data/positions/Posição Consolidada - 5166121.xlsx
+++ b/data/positions/Posição Consolidada - 5166121.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 5166121 | 27/10/2026, 19:01</x:t>
+    <x:t>Conta: 5166121 | 29/10/2026, 16:10</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,13 +34,13 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>11,1%|Renda Fixa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.010.824,76</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11,10%|Pós-Fixada</x:t>
+    <x:t>10,6%|Renda Fixa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.012.469,32</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10,50%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -94,13 +94,13 @@
     <x:t>R$ 2.004.259,95</x:t>
   </x:si>
   <x:si>
-    <x:t>32,6%|Operações Compromissadas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.874.111,08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>32,50%|Pós-Fixada</x:t>
+    <x:t>30,8%|Operações Compromissadas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.879.183,76</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30,80%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>28/09/2026</x:t>
@@ -118,10 +118,10 @@
     <x:t>R$ 846.079,84</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 853.414,89</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 851.764,50</x:t>
+    <x:t>R$ 854.151,89</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 852.335,68</x:t>
   </x:si>
   <x:si>
     <x:t>01/10/2026</x:t>
@@ -136,10 +136,10 @@
     <x:t>R$ 1.500.000,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.511.046,40</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.508.560,96</x:t>
+    <x:t>R$ 1.512.351,31</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.509.572,27</x:t>
   </x:si>
   <x:si>
     <x:t>07/10/2026</x:t>
@@ -154,10 +154,10 @@
     <x:t>R$ 999.998,39</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.005.625,01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.004.359,02</x:t>
+    <x:t>R$ 1.006.493,45</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.005.032,06</x:t>
   </x:si>
   <x:si>
     <x:t>21/10/2026</x:t>
@@ -172,10 +172,10 @@
     <x:t>R$ 1.001.000,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.002.729,42</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.002.340,30</x:t>
+    <x:t>R$ 1.003.595,25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.003.011,32</x:t>
   </x:si>
   <x:si>
     <x:t>23/10/2026</x:t>
@@ -187,19 +187,19 @@
     <x:t>914.634,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.501.295,37</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.501.003,91</x:t>
-  </x:si>
-  <x:si>
-    <x:t>56,3%|Fundos de Investimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 10.159.631,83</x:t>
-  </x:si>
-  <x:si>
-    <x:t>56,30%|Fundos de Renda Fixa Pós-Fixado</x:t>
+    <x:t>R$ 1.502.591,86</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.502.008,69</x:t>
+  </x:si>
+  <x:si>
+    <x:t>58,6%|Fundos de Investimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 11.170.133,77</x:t>
+  </x:si>
+  <x:si>
+    <x:t>58,50%|Fundos de Renda Fixa Pós-Fixado</x:t>
   </x:si>
   <x:si>
     <x:t>Data cota</x:t>
@@ -217,10 +217,10 @@
     <x:t>Safra DI Master FIRF Referenciado DI LP</x:t>
   </x:si>
   <x:si>
-    <x:t>27/10/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 278,22</x:t>
+    <x:t>29/10/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 278,48</x:t>
   </x:si>
   <x:si>
     <x:t>10.972,10</x:t>
@@ -229,10 +229,10 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 3.052.610,53</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 3.038.951,85</x:t>
+    <x:t>R$ 3.055.517,61</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 3.041.024,63</x:t>
   </x:si>
   <x:si>
     <x:t>XP Bancos FIRF Referenciada DI CP RL</x:t>
@@ -244,25 +244,25 @@
     <x:t>1.538.134,23</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 3.031.240,66</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 3.022.067,25</x:t>
+    <x:t>R$ 3.034.283,16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 3.024.239,14</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.472,21</x:t>
+    <x:t>R$ 1.473,65</x:t>
   </x:si>
   <x:si>
     <x:t>2.072,46</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 3.051.079,63</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 3.037.833,32</x:t>
+    <x:t>R$ 3.054.075,37</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 3.039.954,75</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
@@ -271,13 +271,13 @@
     <x:t>R$ 1,51</x:t>
   </x:si>
   <x:si>
-    <x:t>680.719,86</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.024.701,01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.019.143,29</x:t>
+    <x:t>1.344.686,74</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.026.257,63</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.019.972,75</x:t>
   </x:si>
   <x:si>
     <x:t>R$ 837,22</x:t>
@@ -918,10 +918,10 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>18045404.8930348</x:v>
+        <x:v>19062624.0703185</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>18044567.6730348</x:v>
+        <x:v>19061786.8503186</x:v>
       </x:c>
       <x:c r="C4" s="7">
         <x:v>837.22</x:v>
